--- a/www/CLE Instructions and Data Dictionary.xlsx
+++ b/www/CLE Instructions and Data Dictionary.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\CE_Data_Toolkit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5F60BAC1-A5AC-4B27-A4AB-D90D718E8C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE5F895-089F-452D-80B3-74732EC7DA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{51E25282-ACA6-44F1-BA60-C197611A1412}"/>
+    <workbookView xWindow="3912" yWindow="1680" windowWidth="17280" windowHeight="9024" firstSheet="1" activeTab="1" xr2:uid="{51E25282-ACA6-44F1-BA60-C197611A1412}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="2" r:id="rId1"/>
-    <sheet name="Data Dictionary" sheetId="3" r:id="rId2"/>
+    <sheet name="Metadata" sheetId="4" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet name="Data Dictionary" sheetId="3" r:id="rId3"/>
+    <sheet name="Client Details" sheetId="8" r:id="rId4"/>
+    <sheet name="Monthly Statuses" sheetId="9" r:id="rId5"/>
+    <sheet name="Adjusted Enrollments" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -869,7 +873,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1033,6 +1037,14 @@
       <b/>
       <u/>
       <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1386,9 +1398,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1423,6 +1434,8 @@
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1468,7 +1481,45 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1797,982 +1848,6755 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{632E2444-FA30-40DB-BC6E-25FCCB3B0B9C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.21875" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D7F726-B707-4567-9C72-1AA0E898E5EA}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="133.42578125" customWidth="1"/>
+    <col min="1" max="1" width="133.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="9"/>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="9"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="9"/>
-    </row>
-    <row r="5" spans="1:2" ht="24" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="8"/>
+    </row>
+    <row r="5" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A5" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="9"/>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="9"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="9"/>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B6" s="8"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="8"/>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B8" s="9"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="9"/>
-    </row>
-    <row r="10" spans="1:2" ht="24" x14ac:dyDescent="0.4">
-      <c r="A10" s="13" t="s">
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="8"/>
+    </row>
+    <row r="10" spans="1:2" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A10" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="9"/>
-    </row>
-    <row r="11" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="9"/>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="9"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="9"/>
-    </row>
-    <row r="14" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="B12" s="8"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="8"/>
+    </row>
+    <row r="14" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="9"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="B14" s="8"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="9"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="8"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="9"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="8"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="9"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="B17" s="8"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="9"/>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B19" s="8"/>
+    </row>
+    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="9"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="9"/>
-    </row>
-    <row r="22" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="B20" s="8"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
+      <c r="B21" s="8"/>
+    </row>
+    <row r="22" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="9"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="B22" s="8"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="9"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="B23" s="8"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="9"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="9"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="9"/>
-    </row>
-    <row r="27" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="B25" s="8"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="8"/>
+    </row>
+    <row r="27" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="9"/>
-    </row>
-    <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B27" s="8"/>
+    </row>
+    <row r="28" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="5"/>
-    </row>
-    <row r="29" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-    </row>
-    <row r="30" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="30" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B30" s="10"/>
-    </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="B30" s="9"/>
+    </row>
+    <row r="31" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="10"/>
-    </row>
-    <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="B31" s="9"/>
+    </row>
+    <row r="32" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="10"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="9"/>
-    </row>
-    <row r="34" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="B32" s="9"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="9"/>
-    </row>
-    <row r="35" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="B34" s="8"/>
+    </row>
+    <row r="35" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B35" s="9"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-    </row>
-    <row r="37" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="8"/>
+    </row>
+    <row r="37" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="9"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="B37" s="8"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="9"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="B38" s="8"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="9"/>
-    </row>
-    <row r="40" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="B39" s="8"/>
+    </row>
+    <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="9"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="9"/>
-    </row>
-    <row r="42" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="B40" s="8"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
+      <c r="B41" s="8"/>
+    </row>
+    <row r="42" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B42" s="9"/>
-    </row>
-    <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="B42" s="8"/>
+    </row>
+    <row r="43" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="9"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="9"/>
-    </row>
-    <row r="45" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="B43" s="8"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="8"/>
+    </row>
+    <row r="45" spans="1:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="9"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
+      <c r="B45" s="8"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="9"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="B46" s="8"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="9"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3"/>
-      <c r="B48" s="9"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3"/>
-      <c r="B49" s="9"/>
+      <c r="B47" s="8"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="8"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D935D72-FDBC-4B47-8980-B7A328509187}">
   <dimension ref="A1:C63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="39.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>126</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>142</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>148</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>150</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>152</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>68</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>64</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>72</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>64</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>73</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>77</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>78</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>79</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>82</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>80</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>80</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>91</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>80</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>93</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>94</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>163</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>161</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>164</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F7E290-88ED-4847-A59F-DF9F3C813299}">
+  <dimension ref="AU1:BG739"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="23" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="17" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="15.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="47:59" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU2" s="14"/>
+      <c r="AX2" s="14"/>
+      <c r="BD2" s="14"/>
+      <c r="BG2" s="14"/>
+    </row>
+    <row r="3" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU3" s="14"/>
+      <c r="AX3" s="14"/>
+      <c r="BD3" s="14"/>
+      <c r="BG3" s="14"/>
+    </row>
+    <row r="4" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU4" s="14"/>
+      <c r="AX4" s="14"/>
+      <c r="BD4" s="14"/>
+      <c r="BG4" s="14"/>
+    </row>
+    <row r="5" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU5" s="14"/>
+      <c r="AW5" s="14"/>
+      <c r="AX5" s="14"/>
+      <c r="BD5" s="14"/>
+      <c r="BF5" s="14"/>
+      <c r="BG5" s="14"/>
+    </row>
+    <row r="6" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU6" s="14"/>
+      <c r="AX6" s="14"/>
+      <c r="BD6" s="14"/>
+      <c r="BG6" s="14"/>
+    </row>
+    <row r="7" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU7" s="14"/>
+      <c r="AX7" s="14"/>
+      <c r="BD7" s="14"/>
+      <c r="BG7" s="14"/>
+    </row>
+    <row r="8" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU8" s="14"/>
+      <c r="AX8" s="14"/>
+      <c r="BD8" s="14"/>
+      <c r="BG8" s="14"/>
+    </row>
+    <row r="9" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU9" s="14"/>
+      <c r="AX9" s="14"/>
+      <c r="BD9" s="14"/>
+      <c r="BG9" s="14"/>
+    </row>
+    <row r="10" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU10" s="14"/>
+      <c r="AX10" s="14"/>
+      <c r="BD10" s="14"/>
+      <c r="BG10" s="14"/>
+    </row>
+    <row r="11" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU11" s="14"/>
+      <c r="AX11" s="14"/>
+      <c r="BD11" s="14"/>
+      <c r="BG11" s="14"/>
+    </row>
+    <row r="12" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU12" s="14"/>
+      <c r="AX12" s="14"/>
+      <c r="BD12" s="14"/>
+      <c r="BG12" s="14"/>
+    </row>
+    <row r="13" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU13" s="14"/>
+      <c r="AX13" s="14"/>
+      <c r="BD13" s="14"/>
+      <c r="BG13" s="14"/>
+    </row>
+    <row r="14" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU14" s="14"/>
+      <c r="AX14" s="14"/>
+      <c r="BD14" s="14"/>
+      <c r="BG14" s="14"/>
+    </row>
+    <row r="15" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU15" s="14"/>
+      <c r="AX15" s="14"/>
+      <c r="BD15" s="14"/>
+      <c r="BG15" s="14"/>
+    </row>
+    <row r="16" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU16" s="14"/>
+      <c r="AX16" s="14"/>
+      <c r="BD16" s="14"/>
+      <c r="BG16" s="14"/>
+    </row>
+    <row r="17" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU17" s="14"/>
+      <c r="AX17" s="14"/>
+      <c r="BD17" s="14"/>
+      <c r="BG17" s="14"/>
+    </row>
+    <row r="18" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU18" s="14"/>
+      <c r="AX18" s="14"/>
+      <c r="BD18" s="14"/>
+      <c r="BG18" s="14"/>
+    </row>
+    <row r="19" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU19" s="14"/>
+      <c r="AX19" s="14"/>
+      <c r="BD19" s="14"/>
+      <c r="BG19" s="14"/>
+    </row>
+    <row r="20" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU20" s="14"/>
+      <c r="AX20" s="14"/>
+      <c r="BD20" s="14"/>
+      <c r="BG20" s="14"/>
+    </row>
+    <row r="21" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU21" s="14"/>
+      <c r="AX21" s="14"/>
+      <c r="BD21" s="14"/>
+      <c r="BG21" s="14"/>
+    </row>
+    <row r="22" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU22" s="14"/>
+      <c r="AX22" s="14"/>
+      <c r="BD22" s="14"/>
+      <c r="BG22" s="14"/>
+    </row>
+    <row r="23" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU23" s="14"/>
+      <c r="AX23" s="14"/>
+      <c r="BD23" s="14"/>
+      <c r="BG23" s="14"/>
+    </row>
+    <row r="24" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU24" s="14"/>
+      <c r="AX24" s="14"/>
+      <c r="BD24" s="14"/>
+      <c r="BG24" s="14"/>
+    </row>
+    <row r="25" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU25" s="14"/>
+      <c r="AX25" s="14"/>
+      <c r="BD25" s="14"/>
+      <c r="BG25" s="14"/>
+    </row>
+    <row r="26" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU26" s="14"/>
+      <c r="AX26" s="14"/>
+      <c r="BD26" s="14"/>
+      <c r="BG26" s="14"/>
+    </row>
+    <row r="27" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU27" s="14"/>
+      <c r="AX27" s="14"/>
+      <c r="BD27" s="14"/>
+      <c r="BG27" s="14"/>
+    </row>
+    <row r="28" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU28" s="14"/>
+      <c r="AX28" s="14"/>
+      <c r="BD28" s="14"/>
+      <c r="BG28" s="14"/>
+    </row>
+    <row r="29" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU29" s="14"/>
+      <c r="AX29" s="14"/>
+      <c r="BD29" s="14"/>
+      <c r="BG29" s="14"/>
+    </row>
+    <row r="30" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU30" s="14"/>
+      <c r="AX30" s="14"/>
+      <c r="BD30" s="14"/>
+      <c r="BG30" s="14"/>
+    </row>
+    <row r="31" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU31" s="14"/>
+      <c r="AX31" s="14"/>
+      <c r="BD31" s="14"/>
+      <c r="BG31" s="14"/>
+    </row>
+    <row r="32" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU32" s="14"/>
+      <c r="AX32" s="14"/>
+      <c r="BD32" s="14"/>
+      <c r="BG32" s="14"/>
+    </row>
+    <row r="33" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU33" s="14"/>
+      <c r="AX33" s="14"/>
+      <c r="BD33" s="14"/>
+      <c r="BG33" s="14"/>
+    </row>
+    <row r="34" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU34" s="14"/>
+      <c r="AX34" s="14"/>
+      <c r="BD34" s="14"/>
+      <c r="BG34" s="14"/>
+    </row>
+    <row r="35" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU35" s="14"/>
+      <c r="AX35" s="14"/>
+      <c r="BD35" s="14"/>
+      <c r="BG35" s="14"/>
+    </row>
+    <row r="36" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU36" s="14"/>
+      <c r="AX36" s="14"/>
+      <c r="BD36" s="14"/>
+      <c r="BG36" s="14"/>
+    </row>
+    <row r="37" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU37" s="14"/>
+      <c r="AX37" s="14"/>
+      <c r="BD37" s="14"/>
+      <c r="BG37" s="14"/>
+    </row>
+    <row r="38" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU38" s="14"/>
+      <c r="AX38" s="14"/>
+      <c r="BD38" s="14"/>
+      <c r="BG38" s="14"/>
+    </row>
+    <row r="39" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU39" s="14"/>
+      <c r="AX39" s="14"/>
+      <c r="BD39" s="14"/>
+      <c r="BG39" s="14"/>
+    </row>
+    <row r="40" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU40" s="14"/>
+      <c r="AW40" s="14"/>
+      <c r="AX40" s="14"/>
+      <c r="BD40" s="14"/>
+      <c r="BF40" s="14"/>
+      <c r="BG40" s="14"/>
+    </row>
+    <row r="41" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU41" s="14"/>
+      <c r="AX41" s="14"/>
+      <c r="BD41" s="14"/>
+      <c r="BG41" s="14"/>
+    </row>
+    <row r="42" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU42" s="14"/>
+      <c r="AX42" s="14"/>
+      <c r="BD42" s="14"/>
+      <c r="BG42" s="14"/>
+    </row>
+    <row r="43" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU43" s="14"/>
+      <c r="AX43" s="14"/>
+      <c r="BD43" s="14"/>
+      <c r="BG43" s="14"/>
+    </row>
+    <row r="44" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU44" s="14"/>
+      <c r="AX44" s="14"/>
+      <c r="BD44" s="14"/>
+      <c r="BG44" s="14"/>
+    </row>
+    <row r="45" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU45" s="14"/>
+      <c r="AX45" s="14"/>
+      <c r="BD45" s="14"/>
+      <c r="BG45" s="14"/>
+    </row>
+    <row r="46" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU46" s="14"/>
+      <c r="AX46" s="14"/>
+      <c r="BD46" s="14"/>
+      <c r="BG46" s="14"/>
+    </row>
+    <row r="47" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU47" s="14"/>
+      <c r="AX47" s="14"/>
+      <c r="BD47" s="14"/>
+      <c r="BG47" s="14"/>
+    </row>
+    <row r="48" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU48" s="14"/>
+      <c r="AX48" s="14"/>
+      <c r="BD48" s="14"/>
+      <c r="BG48" s="14"/>
+    </row>
+    <row r="49" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU49" s="14"/>
+      <c r="AX49" s="14"/>
+      <c r="BD49" s="14"/>
+      <c r="BG49" s="14"/>
+    </row>
+    <row r="50" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU50" s="14"/>
+      <c r="AX50" s="14"/>
+      <c r="BD50" s="14"/>
+      <c r="BG50" s="14"/>
+    </row>
+    <row r="51" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU51" s="14"/>
+      <c r="AW51" s="14"/>
+      <c r="AX51" s="14"/>
+      <c r="BD51" s="14"/>
+      <c r="BF51" s="14"/>
+      <c r="BG51" s="14"/>
+    </row>
+    <row r="52" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU52" s="14"/>
+      <c r="AX52" s="14"/>
+      <c r="BD52" s="14"/>
+      <c r="BG52" s="14"/>
+    </row>
+    <row r="53" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU53" s="14"/>
+      <c r="AX53" s="14"/>
+      <c r="BD53" s="14"/>
+      <c r="BG53" s="14"/>
+    </row>
+    <row r="54" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU54" s="14"/>
+      <c r="AX54" s="14"/>
+      <c r="BD54" s="14"/>
+      <c r="BG54" s="14"/>
+    </row>
+    <row r="55" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU55" s="14"/>
+      <c r="AX55" s="14"/>
+      <c r="BD55" s="14"/>
+      <c r="BG55" s="14"/>
+    </row>
+    <row r="56" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU56" s="14"/>
+      <c r="AX56" s="14"/>
+      <c r="BD56" s="14"/>
+      <c r="BG56" s="14"/>
+    </row>
+    <row r="57" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU57" s="14"/>
+      <c r="AX57" s="14"/>
+      <c r="BD57" s="14"/>
+      <c r="BG57" s="14"/>
+    </row>
+    <row r="58" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU58" s="14"/>
+      <c r="AX58" s="14"/>
+      <c r="BD58" s="14"/>
+      <c r="BG58" s="14"/>
+    </row>
+    <row r="59" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU59" s="14"/>
+      <c r="AX59" s="14"/>
+      <c r="BD59" s="14"/>
+      <c r="BG59" s="14"/>
+    </row>
+    <row r="60" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU60" s="14"/>
+      <c r="AX60" s="14"/>
+      <c r="BD60" s="14"/>
+      <c r="BG60" s="14"/>
+    </row>
+    <row r="61" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU61" s="14"/>
+      <c r="AX61" s="14"/>
+      <c r="BD61" s="14"/>
+      <c r="BG61" s="14"/>
+    </row>
+    <row r="62" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU62" s="14"/>
+      <c r="AX62" s="14"/>
+      <c r="BD62" s="14"/>
+      <c r="BG62" s="14"/>
+    </row>
+    <row r="63" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU63" s="14"/>
+      <c r="AX63" s="14"/>
+      <c r="BD63" s="14"/>
+      <c r="BG63" s="14"/>
+    </row>
+    <row r="64" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU64" s="14"/>
+      <c r="AX64" s="14"/>
+      <c r="BD64" s="14"/>
+      <c r="BG64" s="14"/>
+    </row>
+    <row r="65" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU65" s="14"/>
+      <c r="AX65" s="14"/>
+      <c r="BD65" s="14"/>
+      <c r="BG65" s="14"/>
+    </row>
+    <row r="66" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU66" s="14"/>
+      <c r="AX66" s="14"/>
+      <c r="BD66" s="14"/>
+      <c r="BG66" s="14"/>
+    </row>
+    <row r="67" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU67" s="14"/>
+      <c r="AX67" s="14"/>
+      <c r="BD67" s="14"/>
+      <c r="BG67" s="14"/>
+    </row>
+    <row r="68" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU68" s="14"/>
+      <c r="AX68" s="14"/>
+      <c r="BD68" s="14"/>
+      <c r="BG68" s="14"/>
+    </row>
+    <row r="69" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU69" s="14"/>
+      <c r="AX69" s="14"/>
+      <c r="BD69" s="14"/>
+      <c r="BG69" s="14"/>
+    </row>
+    <row r="70" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU70" s="14"/>
+      <c r="AX70" s="14"/>
+      <c r="BD70" s="14"/>
+      <c r="BG70" s="14"/>
+    </row>
+    <row r="71" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU71" s="14"/>
+      <c r="AX71" s="14"/>
+      <c r="BD71" s="14"/>
+      <c r="BG71" s="14"/>
+    </row>
+    <row r="72" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU72" s="14"/>
+      <c r="AX72" s="14"/>
+      <c r="BD72" s="14"/>
+      <c r="BG72" s="14"/>
+    </row>
+    <row r="73" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU73" s="14"/>
+      <c r="AX73" s="14"/>
+      <c r="BD73" s="14"/>
+      <c r="BG73" s="14"/>
+    </row>
+    <row r="74" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU74" s="14"/>
+      <c r="AX74" s="14"/>
+      <c r="BD74" s="14"/>
+      <c r="BG74" s="14"/>
+    </row>
+    <row r="75" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU75" s="14"/>
+      <c r="AX75" s="14"/>
+      <c r="BD75" s="14"/>
+      <c r="BG75" s="14"/>
+    </row>
+    <row r="76" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU76" s="14"/>
+      <c r="AX76" s="14"/>
+      <c r="BD76" s="14"/>
+      <c r="BG76" s="14"/>
+    </row>
+    <row r="77" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU77" s="14"/>
+      <c r="AX77" s="14"/>
+      <c r="BD77" s="14"/>
+      <c r="BG77" s="14"/>
+    </row>
+    <row r="78" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU78" s="14"/>
+      <c r="AW78" s="14"/>
+      <c r="AX78" s="14"/>
+      <c r="BD78" s="14"/>
+      <c r="BF78" s="14"/>
+      <c r="BG78" s="14"/>
+    </row>
+    <row r="79" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU79" s="14"/>
+      <c r="AX79" s="14"/>
+      <c r="BD79" s="14"/>
+      <c r="BF79" s="14"/>
+      <c r="BG79" s="14"/>
+    </row>
+    <row r="80" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU80" s="14"/>
+      <c r="AX80" s="14"/>
+      <c r="BD80" s="14"/>
+      <c r="BF80" s="14"/>
+      <c r="BG80" s="14"/>
+    </row>
+    <row r="81" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU81" s="14"/>
+      <c r="AX81" s="14"/>
+      <c r="BD81" s="14"/>
+      <c r="BF81" s="14"/>
+      <c r="BG81" s="14"/>
+    </row>
+    <row r="82" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU82" s="14"/>
+      <c r="AX82" s="14"/>
+      <c r="BD82" s="14"/>
+      <c r="BF82" s="14"/>
+      <c r="BG82" s="14"/>
+    </row>
+    <row r="83" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU83" s="14"/>
+      <c r="AX83" s="14"/>
+      <c r="BD83" s="14"/>
+      <c r="BG83" s="14"/>
+    </row>
+    <row r="84" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU84" s="14"/>
+      <c r="AX84" s="14"/>
+      <c r="BD84" s="14"/>
+      <c r="BG84" s="14"/>
+    </row>
+    <row r="85" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU85" s="14"/>
+      <c r="AX85" s="14"/>
+      <c r="BD85" s="14"/>
+      <c r="BG85" s="14"/>
+    </row>
+    <row r="86" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU86" s="14"/>
+      <c r="AX86" s="14"/>
+      <c r="BD86" s="14"/>
+      <c r="BG86" s="14"/>
+    </row>
+    <row r="87" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU87" s="14"/>
+      <c r="AX87" s="14"/>
+      <c r="BD87" s="14"/>
+      <c r="BG87" s="14"/>
+    </row>
+    <row r="88" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU88" s="14"/>
+      <c r="AW88" s="14"/>
+      <c r="AX88" s="14"/>
+      <c r="BD88" s="14"/>
+      <c r="BF88" s="14"/>
+      <c r="BG88" s="14"/>
+    </row>
+    <row r="89" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU89" s="14"/>
+      <c r="AX89" s="14"/>
+      <c r="BD89" s="14"/>
+      <c r="BG89" s="14"/>
+    </row>
+    <row r="90" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU90" s="14"/>
+      <c r="AX90" s="14"/>
+      <c r="BD90" s="14"/>
+      <c r="BG90" s="14"/>
+    </row>
+    <row r="91" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU91" s="14"/>
+      <c r="AW91" s="14"/>
+      <c r="AX91" s="14"/>
+      <c r="BD91" s="14"/>
+      <c r="BF91" s="14"/>
+      <c r="BG91" s="14"/>
+    </row>
+    <row r="92" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU92" s="14"/>
+      <c r="AX92" s="14"/>
+      <c r="BD92" s="14"/>
+      <c r="BG92" s="14"/>
+    </row>
+    <row r="93" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU93" s="14"/>
+      <c r="AX93" s="14"/>
+      <c r="BD93" s="14"/>
+      <c r="BG93" s="14"/>
+    </row>
+    <row r="94" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU94" s="14"/>
+      <c r="AX94" s="14"/>
+      <c r="BD94" s="14"/>
+      <c r="BG94" s="14"/>
+    </row>
+    <row r="95" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU95" s="14"/>
+      <c r="AX95" s="14"/>
+      <c r="BD95" s="14"/>
+      <c r="BG95" s="14"/>
+    </row>
+    <row r="96" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU96" s="14"/>
+      <c r="AX96" s="14"/>
+      <c r="BD96" s="14"/>
+      <c r="BG96" s="14"/>
+    </row>
+    <row r="97" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU97" s="14"/>
+      <c r="AX97" s="14"/>
+      <c r="BD97" s="14"/>
+      <c r="BG97" s="14"/>
+    </row>
+    <row r="98" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU98" s="14"/>
+      <c r="AW98" s="14"/>
+      <c r="AX98" s="14"/>
+      <c r="BD98" s="14"/>
+      <c r="BF98" s="14"/>
+      <c r="BG98" s="14"/>
+    </row>
+    <row r="99" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU99" s="14"/>
+      <c r="AX99" s="14"/>
+      <c r="BD99" s="14"/>
+      <c r="BG99" s="14"/>
+    </row>
+    <row r="100" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU100" s="14"/>
+      <c r="AX100" s="14"/>
+      <c r="BD100" s="14"/>
+      <c r="BG100" s="14"/>
+    </row>
+    <row r="101" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU101" s="14"/>
+      <c r="AX101" s="14"/>
+      <c r="BD101" s="14"/>
+      <c r="BG101" s="14"/>
+    </row>
+    <row r="102" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU102" s="14"/>
+      <c r="AX102" s="14"/>
+      <c r="BD102" s="14"/>
+      <c r="BG102" s="14"/>
+    </row>
+    <row r="103" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU103" s="14"/>
+      <c r="AX103" s="14"/>
+      <c r="BD103" s="14"/>
+      <c r="BG103" s="14"/>
+    </row>
+    <row r="104" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU104" s="14"/>
+      <c r="AX104" s="14"/>
+      <c r="BD104" s="14"/>
+      <c r="BG104" s="14"/>
+    </row>
+    <row r="105" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU105" s="14"/>
+      <c r="AX105" s="14"/>
+      <c r="BD105" s="14"/>
+      <c r="BG105" s="14"/>
+    </row>
+    <row r="106" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU106" s="14"/>
+      <c r="AW106" s="14"/>
+      <c r="AX106" s="14"/>
+      <c r="BD106" s="14"/>
+      <c r="BF106" s="14"/>
+      <c r="BG106" s="14"/>
+    </row>
+    <row r="107" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU107" s="14"/>
+      <c r="AX107" s="14"/>
+      <c r="BD107" s="14"/>
+      <c r="BG107" s="14"/>
+    </row>
+    <row r="108" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU108" s="14"/>
+      <c r="AX108" s="14"/>
+      <c r="BD108" s="14"/>
+      <c r="BG108" s="14"/>
+    </row>
+    <row r="109" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU109" s="14"/>
+      <c r="AX109" s="14"/>
+      <c r="BD109" s="14"/>
+      <c r="BG109" s="14"/>
+    </row>
+    <row r="110" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU110" s="14"/>
+      <c r="AW110" s="14"/>
+      <c r="AX110" s="14"/>
+      <c r="BD110" s="14"/>
+      <c r="BF110" s="14"/>
+      <c r="BG110" s="14"/>
+    </row>
+    <row r="111" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU111" s="14"/>
+      <c r="AX111" s="14"/>
+      <c r="BD111" s="14"/>
+      <c r="BG111" s="14"/>
+    </row>
+    <row r="112" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU112" s="14"/>
+      <c r="AW112" s="14"/>
+      <c r="AX112" s="14"/>
+      <c r="BD112" s="14"/>
+      <c r="BF112" s="14"/>
+      <c r="BG112" s="14"/>
+    </row>
+    <row r="113" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU113" s="14"/>
+      <c r="AW113" s="14"/>
+      <c r="AX113" s="14"/>
+      <c r="BD113" s="14"/>
+      <c r="BF113" s="14"/>
+      <c r="BG113" s="14"/>
+    </row>
+    <row r="114" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU114" s="14"/>
+      <c r="AX114" s="14"/>
+      <c r="BD114" s="14"/>
+      <c r="BG114" s="14"/>
+    </row>
+    <row r="115" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU115" s="14"/>
+      <c r="AX115" s="14"/>
+      <c r="BD115" s="14"/>
+      <c r="BG115" s="14"/>
+    </row>
+    <row r="116" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU116" s="14"/>
+      <c r="AX116" s="14"/>
+      <c r="BD116" s="14"/>
+      <c r="BG116" s="14"/>
+    </row>
+    <row r="117" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU117" s="14"/>
+      <c r="AX117" s="14"/>
+      <c r="BD117" s="14"/>
+      <c r="BG117" s="14"/>
+    </row>
+    <row r="118" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU118" s="14"/>
+      <c r="AW118" s="14"/>
+      <c r="AX118" s="14"/>
+      <c r="BD118" s="14"/>
+      <c r="BF118" s="14"/>
+      <c r="BG118" s="14"/>
+    </row>
+    <row r="119" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU119" s="14"/>
+      <c r="AW119" s="14"/>
+      <c r="AX119" s="14"/>
+      <c r="BD119" s="14"/>
+      <c r="BF119" s="14"/>
+      <c r="BG119" s="14"/>
+    </row>
+    <row r="120" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU120" s="14"/>
+      <c r="AX120" s="14"/>
+      <c r="BD120" s="14"/>
+      <c r="BG120" s="14"/>
+    </row>
+    <row r="121" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU121" s="14"/>
+      <c r="AX121" s="14"/>
+      <c r="BD121" s="14"/>
+      <c r="BF121" s="14"/>
+      <c r="BG121" s="14"/>
+    </row>
+    <row r="122" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU122" s="14"/>
+      <c r="AX122" s="14"/>
+      <c r="BD122" s="14"/>
+      <c r="BG122" s="14"/>
+    </row>
+    <row r="123" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU123" s="14"/>
+      <c r="AW123" s="14"/>
+      <c r="AX123" s="14"/>
+      <c r="BD123" s="14"/>
+      <c r="BF123" s="14"/>
+      <c r="BG123" s="14"/>
+    </row>
+    <row r="124" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU124" s="14"/>
+      <c r="AX124" s="14"/>
+      <c r="BD124" s="14"/>
+      <c r="BG124" s="14"/>
+    </row>
+    <row r="125" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU125" s="14"/>
+      <c r="AX125" s="14"/>
+      <c r="BD125" s="14"/>
+      <c r="BG125" s="14"/>
+    </row>
+    <row r="126" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU126" s="14"/>
+      <c r="AX126" s="14"/>
+      <c r="BD126" s="14"/>
+      <c r="BG126" s="14"/>
+    </row>
+    <row r="127" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU127" s="14"/>
+      <c r="AX127" s="14"/>
+      <c r="BD127" s="14"/>
+      <c r="BG127" s="14"/>
+    </row>
+    <row r="128" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU128" s="14"/>
+      <c r="AX128" s="14"/>
+      <c r="BD128" s="14"/>
+      <c r="BG128" s="14"/>
+    </row>
+    <row r="129" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU129" s="14"/>
+      <c r="AX129" s="14"/>
+      <c r="BD129" s="14"/>
+      <c r="BG129" s="14"/>
+    </row>
+    <row r="130" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU130" s="14"/>
+      <c r="AX130" s="14"/>
+      <c r="BD130" s="14"/>
+      <c r="BG130" s="14"/>
+    </row>
+    <row r="131" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU131" s="14"/>
+      <c r="AX131" s="14"/>
+      <c r="BD131" s="14"/>
+      <c r="BG131" s="14"/>
+    </row>
+    <row r="132" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU132" s="14"/>
+      <c r="AX132" s="14"/>
+      <c r="BD132" s="14"/>
+      <c r="BF132" s="14"/>
+      <c r="BG132" s="14"/>
+    </row>
+    <row r="133" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU133" s="14"/>
+      <c r="AX133" s="14"/>
+      <c r="BD133" s="14"/>
+      <c r="BF133" s="14"/>
+      <c r="BG133" s="14"/>
+    </row>
+    <row r="134" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU134" s="14"/>
+      <c r="AX134" s="14"/>
+      <c r="BD134" s="14"/>
+      <c r="BF134" s="14"/>
+      <c r="BG134" s="14"/>
+    </row>
+    <row r="135" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU135" s="14"/>
+      <c r="AX135" s="14"/>
+      <c r="BD135" s="14"/>
+      <c r="BF135" s="14"/>
+      <c r="BG135" s="14"/>
+    </row>
+    <row r="136" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU136" s="14"/>
+      <c r="AX136" s="14"/>
+      <c r="BD136" s="14"/>
+      <c r="BF136" s="14"/>
+      <c r="BG136" s="14"/>
+    </row>
+    <row r="137" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU137" s="14"/>
+      <c r="AX137" s="14"/>
+      <c r="BD137" s="14"/>
+      <c r="BG137" s="14"/>
+    </row>
+    <row r="138" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU138" s="14"/>
+      <c r="AX138" s="14"/>
+      <c r="BD138" s="14"/>
+      <c r="BG138" s="14"/>
+    </row>
+    <row r="139" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU139" s="14"/>
+      <c r="AX139" s="14"/>
+      <c r="BD139" s="14"/>
+      <c r="BG139" s="14"/>
+    </row>
+    <row r="140" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU140" s="14"/>
+      <c r="AX140" s="14"/>
+      <c r="BD140" s="14"/>
+      <c r="BG140" s="14"/>
+    </row>
+    <row r="141" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU141" s="14"/>
+      <c r="AW141" s="14"/>
+      <c r="AX141" s="14"/>
+      <c r="BD141" s="14"/>
+      <c r="BF141" s="14"/>
+      <c r="BG141" s="14"/>
+    </row>
+    <row r="142" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU142" s="14"/>
+      <c r="AX142" s="14"/>
+      <c r="BD142" s="14"/>
+      <c r="BG142" s="14"/>
+    </row>
+    <row r="143" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU143" s="14"/>
+      <c r="AX143" s="14"/>
+      <c r="BD143" s="14"/>
+      <c r="BG143" s="14"/>
+    </row>
+    <row r="144" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU144" s="14"/>
+      <c r="AX144" s="14"/>
+      <c r="BD144" s="14"/>
+      <c r="BG144" s="14"/>
+    </row>
+    <row r="145" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU145" s="14"/>
+      <c r="AX145" s="14"/>
+      <c r="BD145" s="14"/>
+      <c r="BG145" s="14"/>
+    </row>
+    <row r="146" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU146" s="14"/>
+      <c r="AX146" s="14"/>
+      <c r="BD146" s="14"/>
+      <c r="BG146" s="14"/>
+    </row>
+    <row r="147" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU147" s="14"/>
+      <c r="AX147" s="14"/>
+      <c r="BD147" s="14"/>
+      <c r="BG147" s="14"/>
+    </row>
+    <row r="148" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU148" s="14"/>
+      <c r="AW148" s="14"/>
+      <c r="AX148" s="14"/>
+      <c r="BD148" s="14"/>
+      <c r="BF148" s="14"/>
+      <c r="BG148" s="14"/>
+    </row>
+    <row r="149" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU149" s="14"/>
+      <c r="AW149" s="14"/>
+      <c r="AX149" s="14"/>
+      <c r="BD149" s="14"/>
+      <c r="BF149" s="14"/>
+      <c r="BG149" s="14"/>
+    </row>
+    <row r="150" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU150" s="14"/>
+      <c r="AW150" s="14"/>
+      <c r="AX150" s="14"/>
+      <c r="BD150" s="14"/>
+      <c r="BF150" s="14"/>
+      <c r="BG150" s="14"/>
+    </row>
+    <row r="151" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU151" s="14"/>
+      <c r="AW151" s="14"/>
+      <c r="AX151" s="14"/>
+      <c r="BD151" s="14"/>
+      <c r="BF151" s="14"/>
+      <c r="BG151" s="14"/>
+    </row>
+    <row r="152" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU152" s="14"/>
+      <c r="AX152" s="14"/>
+      <c r="BD152" s="14"/>
+      <c r="BG152" s="14"/>
+    </row>
+    <row r="153" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU153" s="14"/>
+      <c r="AX153" s="14"/>
+      <c r="BD153" s="14"/>
+      <c r="BG153" s="14"/>
+    </row>
+    <row r="154" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU154" s="14"/>
+      <c r="AX154" s="14"/>
+      <c r="BD154" s="14"/>
+      <c r="BG154" s="14"/>
+    </row>
+    <row r="155" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU155" s="14"/>
+      <c r="AX155" s="14"/>
+      <c r="BD155" s="14"/>
+      <c r="BG155" s="14"/>
+    </row>
+    <row r="156" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU156" s="14"/>
+      <c r="AX156" s="14"/>
+      <c r="BD156" s="14"/>
+      <c r="BG156" s="14"/>
+    </row>
+    <row r="157" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU157" s="14"/>
+      <c r="AW157" s="14"/>
+      <c r="AX157" s="14"/>
+      <c r="BD157" s="14"/>
+      <c r="BF157" s="14"/>
+      <c r="BG157" s="14"/>
+    </row>
+    <row r="158" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU158" s="14"/>
+      <c r="AX158" s="14"/>
+      <c r="BD158" s="14"/>
+      <c r="BG158" s="14"/>
+    </row>
+    <row r="159" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU159" s="14"/>
+      <c r="AX159" s="14"/>
+      <c r="BD159" s="14"/>
+      <c r="BG159" s="14"/>
+    </row>
+    <row r="160" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU160" s="14"/>
+      <c r="AW160" s="14"/>
+      <c r="AX160" s="14"/>
+      <c r="BD160" s="14"/>
+      <c r="BF160" s="14"/>
+      <c r="BG160" s="14"/>
+    </row>
+    <row r="161" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU161" s="14"/>
+      <c r="AX161" s="14"/>
+      <c r="BD161" s="14"/>
+      <c r="BG161" s="14"/>
+    </row>
+    <row r="162" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU162" s="14"/>
+      <c r="AX162" s="14"/>
+      <c r="BD162" s="14"/>
+      <c r="BG162" s="14"/>
+    </row>
+    <row r="163" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU163" s="14"/>
+      <c r="AX163" s="14"/>
+      <c r="BD163" s="14"/>
+      <c r="BG163" s="14"/>
+    </row>
+    <row r="164" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU164" s="14"/>
+      <c r="AX164" s="14"/>
+      <c r="BD164" s="14"/>
+      <c r="BG164" s="14"/>
+    </row>
+    <row r="165" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU165" s="14"/>
+      <c r="AX165" s="14"/>
+      <c r="BD165" s="14"/>
+      <c r="BG165" s="14"/>
+    </row>
+    <row r="166" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU166" s="14"/>
+      <c r="AX166" s="14"/>
+      <c r="BD166" s="14"/>
+      <c r="BG166" s="14"/>
+    </row>
+    <row r="167" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU167" s="14"/>
+      <c r="AW167" s="14"/>
+      <c r="AX167" s="14"/>
+      <c r="BD167" s="14"/>
+      <c r="BF167" s="14"/>
+      <c r="BG167" s="14"/>
+    </row>
+    <row r="168" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU168" s="14"/>
+      <c r="AX168" s="14"/>
+      <c r="BD168" s="14"/>
+      <c r="BG168" s="14"/>
+    </row>
+    <row r="169" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU169" s="14"/>
+      <c r="AX169" s="14"/>
+      <c r="BD169" s="14"/>
+      <c r="BG169" s="14"/>
+    </row>
+    <row r="170" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU170" s="14"/>
+      <c r="AW170" s="14"/>
+      <c r="AX170" s="14"/>
+      <c r="BD170" s="14"/>
+      <c r="BF170" s="14"/>
+      <c r="BG170" s="14"/>
+    </row>
+    <row r="171" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU171" s="14"/>
+      <c r="AX171" s="14"/>
+      <c r="BD171" s="14"/>
+      <c r="BG171" s="14"/>
+    </row>
+    <row r="172" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU172" s="14"/>
+      <c r="AX172" s="14"/>
+      <c r="BD172" s="14"/>
+      <c r="BG172" s="14"/>
+    </row>
+    <row r="173" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU173" s="14"/>
+      <c r="AW173" s="14"/>
+      <c r="AX173" s="14"/>
+      <c r="BD173" s="14"/>
+      <c r="BF173" s="14"/>
+      <c r="BG173" s="14"/>
+    </row>
+    <row r="174" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU174" s="14"/>
+      <c r="AX174" s="14"/>
+      <c r="BD174" s="14"/>
+      <c r="BG174" s="14"/>
+    </row>
+    <row r="175" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU175" s="14"/>
+      <c r="AX175" s="14"/>
+      <c r="BD175" s="14"/>
+      <c r="BG175" s="14"/>
+    </row>
+    <row r="176" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU176" s="14"/>
+      <c r="AX176" s="14"/>
+      <c r="BD176" s="14"/>
+      <c r="BG176" s="14"/>
+    </row>
+    <row r="177" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU177" s="14"/>
+      <c r="AX177" s="14"/>
+      <c r="BD177" s="14"/>
+      <c r="BG177" s="14"/>
+    </row>
+    <row r="178" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU178" s="14"/>
+      <c r="AX178" s="14"/>
+      <c r="BD178" s="14"/>
+      <c r="BG178" s="14"/>
+    </row>
+    <row r="179" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU179" s="14"/>
+      <c r="AX179" s="14"/>
+      <c r="BD179" s="14"/>
+      <c r="BG179" s="14"/>
+    </row>
+    <row r="180" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU180" s="14"/>
+      <c r="AX180" s="14"/>
+      <c r="BD180" s="14"/>
+      <c r="BG180" s="14"/>
+    </row>
+    <row r="181" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU181" s="14"/>
+      <c r="AX181" s="14"/>
+      <c r="BD181" s="14"/>
+      <c r="BG181" s="14"/>
+    </row>
+    <row r="182" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU182" s="14"/>
+      <c r="AX182" s="14"/>
+      <c r="BD182" s="14"/>
+      <c r="BG182" s="14"/>
+    </row>
+    <row r="183" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU183" s="14"/>
+      <c r="AX183" s="14"/>
+      <c r="BD183" s="14"/>
+      <c r="BF183" s="14"/>
+      <c r="BG183" s="14"/>
+    </row>
+    <row r="184" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU184" s="14"/>
+      <c r="AW184" s="14"/>
+      <c r="AX184" s="14"/>
+      <c r="BD184" s="14"/>
+      <c r="BF184" s="14"/>
+      <c r="BG184" s="14"/>
+    </row>
+    <row r="185" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU185" s="14"/>
+      <c r="AX185" s="14"/>
+      <c r="BD185" s="14"/>
+      <c r="BF185" s="14"/>
+      <c r="BG185" s="14"/>
+    </row>
+    <row r="186" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU186" s="14"/>
+      <c r="AX186" s="14"/>
+      <c r="BD186" s="14"/>
+      <c r="BG186" s="14"/>
+    </row>
+    <row r="187" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU187" s="14"/>
+      <c r="AX187" s="14"/>
+      <c r="BD187" s="14"/>
+      <c r="BG187" s="14"/>
+    </row>
+    <row r="188" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU188" s="14"/>
+      <c r="AX188" s="14"/>
+      <c r="BD188" s="14"/>
+      <c r="BG188" s="14"/>
+    </row>
+    <row r="189" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU189" s="14"/>
+      <c r="AW189" s="14"/>
+      <c r="AX189" s="14"/>
+      <c r="BD189" s="14"/>
+      <c r="BF189" s="14"/>
+      <c r="BG189" s="14"/>
+    </row>
+    <row r="190" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU190" s="14"/>
+      <c r="AX190" s="14"/>
+      <c r="BD190" s="14"/>
+      <c r="BG190" s="14"/>
+    </row>
+    <row r="191" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU191" s="14"/>
+      <c r="AX191" s="14"/>
+      <c r="BD191" s="14"/>
+      <c r="BG191" s="14"/>
+    </row>
+    <row r="192" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU192" s="14"/>
+      <c r="AX192" s="14"/>
+      <c r="BD192" s="14"/>
+      <c r="BG192" s="14"/>
+    </row>
+    <row r="193" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU193" s="14"/>
+      <c r="AX193" s="14"/>
+      <c r="BD193" s="14"/>
+      <c r="BG193" s="14"/>
+    </row>
+    <row r="194" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU194" s="14"/>
+      <c r="AW194" s="14"/>
+      <c r="AX194" s="14"/>
+      <c r="BD194" s="14"/>
+      <c r="BF194" s="14"/>
+      <c r="BG194" s="14"/>
+    </row>
+    <row r="195" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU195" s="14"/>
+      <c r="AX195" s="14"/>
+      <c r="BD195" s="14"/>
+      <c r="BG195" s="14"/>
+    </row>
+    <row r="196" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU196" s="14"/>
+      <c r="AW196" s="14"/>
+      <c r="AX196" s="14"/>
+      <c r="BD196" s="14"/>
+      <c r="BF196" s="14"/>
+      <c r="BG196" s="14"/>
+    </row>
+    <row r="197" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU197" s="14"/>
+      <c r="AX197" s="14"/>
+      <c r="BD197" s="14"/>
+      <c r="BF197" s="14"/>
+      <c r="BG197" s="14"/>
+    </row>
+    <row r="198" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU198" s="14"/>
+      <c r="AX198" s="14"/>
+      <c r="BD198" s="14"/>
+      <c r="BG198" s="14"/>
+    </row>
+    <row r="199" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU199" s="14"/>
+      <c r="AW199" s="14"/>
+      <c r="AX199" s="14"/>
+      <c r="BD199" s="14"/>
+      <c r="BF199" s="14"/>
+      <c r="BG199" s="14"/>
+    </row>
+    <row r="200" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU200" s="14"/>
+      <c r="AX200" s="14"/>
+      <c r="BD200" s="14"/>
+      <c r="BG200" s="14"/>
+    </row>
+    <row r="201" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU201" s="14"/>
+      <c r="AX201" s="14"/>
+      <c r="BD201" s="14"/>
+      <c r="BG201" s="14"/>
+    </row>
+    <row r="202" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU202" s="14"/>
+      <c r="AX202" s="14"/>
+      <c r="BD202" s="14"/>
+      <c r="BG202" s="14"/>
+    </row>
+    <row r="203" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU203" s="14"/>
+      <c r="AX203" s="14"/>
+      <c r="BD203" s="14"/>
+      <c r="BG203" s="14"/>
+    </row>
+    <row r="204" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU204" s="14"/>
+      <c r="AX204" s="14"/>
+      <c r="BD204" s="14"/>
+      <c r="BG204" s="14"/>
+    </row>
+    <row r="205" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU205" s="14"/>
+      <c r="AX205" s="14"/>
+      <c r="BD205" s="14"/>
+      <c r="BG205" s="14"/>
+    </row>
+    <row r="206" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU206" s="14"/>
+      <c r="AX206" s="14"/>
+      <c r="BD206" s="14"/>
+      <c r="BG206" s="14"/>
+    </row>
+    <row r="207" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU207" s="14"/>
+      <c r="AW207" s="14"/>
+      <c r="AX207" s="14"/>
+      <c r="BD207" s="14"/>
+      <c r="BF207" s="14"/>
+      <c r="BG207" s="14"/>
+    </row>
+    <row r="208" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU208" s="14"/>
+      <c r="AX208" s="14"/>
+      <c r="BD208" s="14"/>
+      <c r="BG208" s="14"/>
+    </row>
+    <row r="209" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU209" s="14"/>
+      <c r="AX209" s="14"/>
+      <c r="BD209" s="14"/>
+      <c r="BG209" s="14"/>
+    </row>
+    <row r="210" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU210" s="14"/>
+      <c r="AW210" s="14"/>
+      <c r="AX210" s="14"/>
+      <c r="BD210" s="14"/>
+      <c r="BF210" s="14"/>
+      <c r="BG210" s="14"/>
+    </row>
+    <row r="211" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU211" s="14"/>
+      <c r="AX211" s="14"/>
+      <c r="BD211" s="14"/>
+      <c r="BG211" s="14"/>
+    </row>
+    <row r="212" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU212" s="14"/>
+      <c r="AX212" s="14"/>
+      <c r="BD212" s="14"/>
+      <c r="BG212" s="14"/>
+    </row>
+    <row r="213" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU213" s="14"/>
+      <c r="AX213" s="14"/>
+      <c r="BD213" s="14"/>
+      <c r="BG213" s="14"/>
+    </row>
+    <row r="214" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU214" s="14"/>
+      <c r="AX214" s="14"/>
+      <c r="BD214" s="14"/>
+      <c r="BG214" s="14"/>
+    </row>
+    <row r="215" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU215" s="14"/>
+      <c r="AW215" s="14"/>
+      <c r="AX215" s="14"/>
+      <c r="BD215" s="14"/>
+      <c r="BF215" s="14"/>
+      <c r="BG215" s="14"/>
+    </row>
+    <row r="216" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU216" s="14"/>
+      <c r="AX216" s="14"/>
+      <c r="BD216" s="14"/>
+      <c r="BF216" s="14"/>
+      <c r="BG216" s="14"/>
+    </row>
+    <row r="217" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU217" s="14"/>
+      <c r="AX217" s="14"/>
+      <c r="BD217" s="14"/>
+      <c r="BF217" s="14"/>
+      <c r="BG217" s="14"/>
+    </row>
+    <row r="218" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU218" s="14"/>
+      <c r="AX218" s="14"/>
+      <c r="BD218" s="14"/>
+      <c r="BG218" s="14"/>
+    </row>
+    <row r="219" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU219" s="14"/>
+      <c r="AX219" s="14"/>
+      <c r="BD219" s="14"/>
+      <c r="BG219" s="14"/>
+    </row>
+    <row r="220" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU220" s="14"/>
+      <c r="AW220" s="14"/>
+      <c r="AX220" s="14"/>
+      <c r="BD220" s="14"/>
+      <c r="BF220" s="14"/>
+      <c r="BG220" s="14"/>
+    </row>
+    <row r="221" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU221" s="14"/>
+      <c r="AX221" s="14"/>
+      <c r="BD221" s="14"/>
+      <c r="BG221" s="14"/>
+    </row>
+    <row r="222" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU222" s="14"/>
+      <c r="AX222" s="14"/>
+      <c r="BD222" s="14"/>
+      <c r="BG222" s="14"/>
+    </row>
+    <row r="223" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU223" s="14"/>
+      <c r="AX223" s="14"/>
+      <c r="BD223" s="14"/>
+      <c r="BG223" s="14"/>
+    </row>
+    <row r="224" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU224" s="14"/>
+      <c r="AW224" s="14"/>
+      <c r="AX224" s="14"/>
+      <c r="BD224" s="14"/>
+      <c r="BF224" s="14"/>
+      <c r="BG224" s="14"/>
+    </row>
+    <row r="225" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU225" s="14"/>
+      <c r="AX225" s="14"/>
+      <c r="BD225" s="14"/>
+      <c r="BG225" s="14"/>
+    </row>
+    <row r="226" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU226" s="14"/>
+      <c r="AW226" s="14"/>
+      <c r="AX226" s="14"/>
+      <c r="BD226" s="14"/>
+      <c r="BF226" s="14"/>
+      <c r="BG226" s="14"/>
+    </row>
+    <row r="227" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU227" s="14"/>
+      <c r="AW227" s="14"/>
+      <c r="AX227" s="14"/>
+      <c r="BD227" s="14"/>
+      <c r="BF227" s="14"/>
+      <c r="BG227" s="14"/>
+    </row>
+    <row r="228" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU228" s="14"/>
+      <c r="AX228" s="14"/>
+      <c r="BD228" s="14"/>
+      <c r="BG228" s="14"/>
+    </row>
+    <row r="229" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU229" s="14"/>
+      <c r="AX229" s="14"/>
+      <c r="BD229" s="14"/>
+      <c r="BG229" s="14"/>
+    </row>
+    <row r="230" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU230" s="14"/>
+      <c r="AX230" s="14"/>
+      <c r="BD230" s="14"/>
+      <c r="BG230" s="14"/>
+    </row>
+    <row r="231" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU231" s="14"/>
+      <c r="AX231" s="14"/>
+      <c r="BD231" s="14"/>
+      <c r="BG231" s="14"/>
+    </row>
+    <row r="232" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU232" s="14"/>
+      <c r="AX232" s="14"/>
+      <c r="BD232" s="14"/>
+      <c r="BF232" s="14"/>
+      <c r="BG232" s="14"/>
+    </row>
+    <row r="233" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU233" s="14"/>
+      <c r="AX233" s="14"/>
+      <c r="BD233" s="14"/>
+      <c r="BG233" s="14"/>
+    </row>
+    <row r="234" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU234" s="14"/>
+      <c r="AX234" s="14"/>
+      <c r="BD234" s="14"/>
+      <c r="BG234" s="14"/>
+    </row>
+    <row r="235" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU235" s="14"/>
+      <c r="AX235" s="14"/>
+      <c r="BD235" s="14"/>
+      <c r="BG235" s="14"/>
+    </row>
+    <row r="236" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU236" s="14"/>
+      <c r="AX236" s="14"/>
+      <c r="BD236" s="14"/>
+      <c r="BG236" s="14"/>
+    </row>
+    <row r="237" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU237" s="14"/>
+      <c r="AX237" s="14"/>
+      <c r="BD237" s="14"/>
+      <c r="BG237" s="14"/>
+    </row>
+    <row r="238" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU238" s="14"/>
+      <c r="AX238" s="14"/>
+      <c r="BD238" s="14"/>
+      <c r="BG238" s="14"/>
+    </row>
+    <row r="239" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU239" s="14"/>
+      <c r="AX239" s="14"/>
+      <c r="BD239" s="14"/>
+      <c r="BG239" s="14"/>
+    </row>
+    <row r="240" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU240" s="14"/>
+      <c r="AW240" s="14"/>
+      <c r="AX240" s="14"/>
+      <c r="BD240" s="14"/>
+      <c r="BF240" s="14"/>
+      <c r="BG240" s="14"/>
+    </row>
+    <row r="241" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU241" s="14"/>
+      <c r="AW241" s="14"/>
+      <c r="AX241" s="14"/>
+      <c r="BD241" s="14"/>
+      <c r="BF241" s="14"/>
+      <c r="BG241" s="14"/>
+    </row>
+    <row r="242" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU242" s="14"/>
+      <c r="AW242" s="14"/>
+      <c r="AX242" s="14"/>
+      <c r="BD242" s="14"/>
+      <c r="BF242" s="14"/>
+      <c r="BG242" s="14"/>
+    </row>
+    <row r="243" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU243" s="14"/>
+      <c r="AX243" s="14"/>
+      <c r="BD243" s="14"/>
+      <c r="BG243" s="14"/>
+    </row>
+    <row r="244" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU244" s="14"/>
+      <c r="AX244" s="14"/>
+      <c r="BD244" s="14"/>
+      <c r="BG244" s="14"/>
+    </row>
+    <row r="245" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU245" s="14"/>
+      <c r="AX245" s="14"/>
+      <c r="BD245" s="14"/>
+      <c r="BG245" s="14"/>
+    </row>
+    <row r="246" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU246" s="14"/>
+      <c r="AX246" s="14"/>
+      <c r="BD246" s="14"/>
+      <c r="BG246" s="14"/>
+    </row>
+    <row r="247" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU247" s="14"/>
+      <c r="AW247" s="14"/>
+      <c r="AX247" s="14"/>
+      <c r="BD247" s="14"/>
+      <c r="BG247" s="14"/>
+    </row>
+    <row r="248" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU248" s="14"/>
+      <c r="AX248" s="14"/>
+      <c r="BD248" s="14"/>
+      <c r="BG248" s="14"/>
+    </row>
+    <row r="249" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU249" s="14"/>
+      <c r="AX249" s="14"/>
+      <c r="BD249" s="14"/>
+      <c r="BG249" s="14"/>
+    </row>
+    <row r="250" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU250" s="14"/>
+      <c r="AX250" s="14"/>
+      <c r="BD250" s="14"/>
+      <c r="BG250" s="14"/>
+    </row>
+    <row r="251" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU251" s="14"/>
+      <c r="AW251" s="14"/>
+      <c r="AX251" s="14"/>
+      <c r="BD251" s="14"/>
+      <c r="BF251" s="14"/>
+      <c r="BG251" s="14"/>
+    </row>
+    <row r="252" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU252" s="14"/>
+      <c r="AX252" s="14"/>
+      <c r="BD252" s="14"/>
+      <c r="BG252" s="14"/>
+    </row>
+    <row r="253" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU253" s="14"/>
+      <c r="AX253" s="14"/>
+      <c r="BD253" s="14"/>
+      <c r="BG253" s="14"/>
+    </row>
+    <row r="254" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU254" s="14"/>
+      <c r="AW254" s="14"/>
+      <c r="AX254" s="14"/>
+      <c r="BD254" s="14"/>
+      <c r="BF254" s="14"/>
+      <c r="BG254" s="14"/>
+    </row>
+    <row r="255" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU255" s="14"/>
+      <c r="AX255" s="14"/>
+      <c r="BD255" s="14"/>
+      <c r="BG255" s="14"/>
+    </row>
+    <row r="256" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU256" s="14"/>
+      <c r="AX256" s="14"/>
+      <c r="BD256" s="14"/>
+      <c r="BG256" s="14"/>
+    </row>
+    <row r="257" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU257" s="14"/>
+      <c r="AX257" s="14"/>
+      <c r="BD257" s="14"/>
+      <c r="BG257" s="14"/>
+    </row>
+    <row r="258" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU258" s="14"/>
+      <c r="AX258" s="14"/>
+      <c r="BD258" s="14"/>
+      <c r="BG258" s="14"/>
+    </row>
+    <row r="259" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU259" s="14"/>
+      <c r="AW259" s="14"/>
+      <c r="AX259" s="14"/>
+      <c r="BD259" s="14"/>
+      <c r="BF259" s="14"/>
+      <c r="BG259" s="14"/>
+    </row>
+    <row r="260" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU260" s="14"/>
+      <c r="AX260" s="14"/>
+      <c r="BD260" s="14"/>
+      <c r="BG260" s="14"/>
+    </row>
+    <row r="261" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU261" s="14"/>
+      <c r="AX261" s="14"/>
+      <c r="BD261" s="14"/>
+      <c r="BG261" s="14"/>
+    </row>
+    <row r="262" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU262" s="14"/>
+      <c r="AX262" s="14"/>
+      <c r="BD262" s="14"/>
+      <c r="BG262" s="14"/>
+    </row>
+    <row r="263" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU263" s="14"/>
+      <c r="AX263" s="14"/>
+      <c r="BD263" s="14"/>
+      <c r="BG263" s="14"/>
+    </row>
+    <row r="264" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU264" s="14"/>
+      <c r="AX264" s="14"/>
+      <c r="BD264" s="14"/>
+      <c r="BG264" s="14"/>
+    </row>
+    <row r="265" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU265" s="14"/>
+      <c r="AX265" s="14"/>
+      <c r="BD265" s="14"/>
+      <c r="BG265" s="14"/>
+    </row>
+    <row r="266" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU266" s="14"/>
+      <c r="AX266" s="14"/>
+      <c r="BD266" s="14"/>
+      <c r="BG266" s="14"/>
+    </row>
+    <row r="267" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU267" s="14"/>
+      <c r="AW267" s="14"/>
+      <c r="AX267" s="14"/>
+      <c r="BD267" s="14"/>
+      <c r="BF267" s="14"/>
+      <c r="BG267" s="14"/>
+    </row>
+    <row r="268" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU268" s="14"/>
+      <c r="AX268" s="14"/>
+      <c r="BD268" s="14"/>
+      <c r="BG268" s="14"/>
+    </row>
+    <row r="269" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU269" s="14"/>
+      <c r="AX269" s="14"/>
+      <c r="BD269" s="14"/>
+      <c r="BG269" s="14"/>
+    </row>
+    <row r="270" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU270" s="14"/>
+      <c r="AX270" s="14"/>
+      <c r="BD270" s="14"/>
+      <c r="BG270" s="14"/>
+    </row>
+    <row r="271" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU271" s="14"/>
+      <c r="AX271" s="14"/>
+      <c r="BD271" s="14"/>
+      <c r="BG271" s="14"/>
+    </row>
+    <row r="272" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU272" s="14"/>
+      <c r="AX272" s="14"/>
+      <c r="BD272" s="14"/>
+      <c r="BG272" s="14"/>
+    </row>
+    <row r="273" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU273" s="14"/>
+      <c r="AX273" s="14"/>
+      <c r="BD273" s="14"/>
+      <c r="BG273" s="14"/>
+    </row>
+    <row r="274" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU274" s="14"/>
+      <c r="AX274" s="14"/>
+      <c r="BD274" s="14"/>
+      <c r="BG274" s="14"/>
+    </row>
+    <row r="275" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU275" s="14"/>
+      <c r="AX275" s="14"/>
+      <c r="BD275" s="14"/>
+      <c r="BG275" s="14"/>
+    </row>
+    <row r="276" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU276" s="14"/>
+      <c r="AX276" s="14"/>
+      <c r="BD276" s="14"/>
+      <c r="BG276" s="14"/>
+    </row>
+    <row r="277" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU277" s="14"/>
+      <c r="AX277" s="14"/>
+      <c r="BD277" s="14"/>
+      <c r="BG277" s="14"/>
+    </row>
+    <row r="278" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU278" s="14"/>
+      <c r="AX278" s="14"/>
+      <c r="BD278" s="14"/>
+      <c r="BG278" s="14"/>
+    </row>
+    <row r="279" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU279" s="14"/>
+      <c r="AX279" s="14"/>
+      <c r="BD279" s="14"/>
+      <c r="BG279" s="14"/>
+    </row>
+    <row r="280" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU280" s="14"/>
+      <c r="AX280" s="14"/>
+      <c r="BD280" s="14"/>
+      <c r="BG280" s="14"/>
+    </row>
+    <row r="281" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU281" s="14"/>
+      <c r="AX281" s="14"/>
+      <c r="BD281" s="14"/>
+      <c r="BG281" s="14"/>
+    </row>
+    <row r="282" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU282" s="14"/>
+      <c r="AX282" s="14"/>
+      <c r="BD282" s="14"/>
+      <c r="BG282" s="14"/>
+    </row>
+    <row r="283" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU283" s="14"/>
+      <c r="AX283" s="14"/>
+      <c r="BD283" s="14"/>
+      <c r="BG283" s="14"/>
+    </row>
+    <row r="284" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU284" s="14"/>
+      <c r="AX284" s="14"/>
+      <c r="BD284" s="14"/>
+      <c r="BG284" s="14"/>
+    </row>
+    <row r="285" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU285" s="14"/>
+      <c r="AX285" s="14"/>
+      <c r="BD285" s="14"/>
+      <c r="BG285" s="14"/>
+    </row>
+    <row r="286" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU286" s="14"/>
+      <c r="AX286" s="14"/>
+      <c r="BD286" s="14"/>
+      <c r="BG286" s="14"/>
+    </row>
+    <row r="287" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU287" s="14"/>
+      <c r="AX287" s="14"/>
+      <c r="BD287" s="14"/>
+      <c r="BG287" s="14"/>
+    </row>
+    <row r="288" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU288" s="14"/>
+      <c r="AX288" s="14"/>
+      <c r="BD288" s="14"/>
+      <c r="BG288" s="14"/>
+    </row>
+    <row r="289" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU289" s="14"/>
+      <c r="AW289" s="14"/>
+      <c r="AX289" s="14"/>
+      <c r="BD289" s="14"/>
+      <c r="BF289" s="14"/>
+      <c r="BG289" s="14"/>
+    </row>
+    <row r="290" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU290" s="14"/>
+      <c r="AW290" s="14"/>
+      <c r="AX290" s="14"/>
+      <c r="BD290" s="14"/>
+      <c r="BF290" s="14"/>
+      <c r="BG290" s="14"/>
+    </row>
+    <row r="291" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU291" s="14"/>
+      <c r="AX291" s="14"/>
+      <c r="BD291" s="14"/>
+      <c r="BG291" s="14"/>
+    </row>
+    <row r="292" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU292" s="14"/>
+      <c r="AX292" s="14"/>
+      <c r="BD292" s="14"/>
+      <c r="BG292" s="14"/>
+    </row>
+    <row r="293" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU293" s="14"/>
+      <c r="AX293" s="14"/>
+      <c r="BD293" s="14"/>
+      <c r="BF293" s="14"/>
+      <c r="BG293" s="14"/>
+    </row>
+    <row r="294" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU294" s="14"/>
+      <c r="AW294" s="14"/>
+      <c r="AX294" s="14"/>
+      <c r="BD294" s="14"/>
+      <c r="BF294" s="14"/>
+      <c r="BG294" s="14"/>
+    </row>
+    <row r="295" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU295" s="14"/>
+      <c r="AW295" s="14"/>
+      <c r="AX295" s="14"/>
+      <c r="BD295" s="14"/>
+      <c r="BF295" s="14"/>
+      <c r="BG295" s="14"/>
+    </row>
+    <row r="296" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU296" s="14"/>
+      <c r="AX296" s="14"/>
+      <c r="BD296" s="14"/>
+      <c r="BG296" s="14"/>
+    </row>
+    <row r="297" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU297" s="14"/>
+      <c r="AX297" s="14"/>
+      <c r="BD297" s="14"/>
+      <c r="BF297" s="14"/>
+      <c r="BG297" s="14"/>
+    </row>
+    <row r="298" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU298" s="14"/>
+      <c r="AX298" s="14"/>
+      <c r="BD298" s="14"/>
+      <c r="BG298" s="14"/>
+    </row>
+    <row r="299" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU299" s="14"/>
+      <c r="AX299" s="14"/>
+      <c r="BD299" s="14"/>
+      <c r="BG299" s="14"/>
+    </row>
+    <row r="300" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU300" s="14"/>
+      <c r="AX300" s="14"/>
+      <c r="BD300" s="14"/>
+      <c r="BG300" s="14"/>
+    </row>
+    <row r="301" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU301" s="14"/>
+      <c r="AX301" s="14"/>
+      <c r="BD301" s="14"/>
+      <c r="BG301" s="14"/>
+    </row>
+    <row r="302" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU302" s="14"/>
+      <c r="AX302" s="14"/>
+      <c r="BD302" s="14"/>
+      <c r="BG302" s="14"/>
+    </row>
+    <row r="303" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU303" s="14"/>
+      <c r="AX303" s="14"/>
+      <c r="BD303" s="14"/>
+      <c r="BG303" s="14"/>
+    </row>
+    <row r="304" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU304" s="14"/>
+      <c r="AX304" s="14"/>
+      <c r="BD304" s="14"/>
+      <c r="BG304" s="14"/>
+    </row>
+    <row r="305" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU305" s="14"/>
+      <c r="AX305" s="14"/>
+      <c r="BD305" s="14"/>
+      <c r="BG305" s="14"/>
+    </row>
+    <row r="306" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU306" s="14"/>
+      <c r="AX306" s="14"/>
+      <c r="BD306" s="14"/>
+      <c r="BG306" s="14"/>
+    </row>
+    <row r="307" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU307" s="14"/>
+      <c r="AX307" s="14"/>
+      <c r="BD307" s="14"/>
+      <c r="BG307" s="14"/>
+    </row>
+    <row r="308" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU308" s="14"/>
+      <c r="AW308" s="14"/>
+      <c r="AX308" s="14"/>
+      <c r="BD308" s="14"/>
+      <c r="BF308" s="14"/>
+      <c r="BG308" s="14"/>
+    </row>
+    <row r="309" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU309" s="14"/>
+      <c r="AW309" s="14"/>
+      <c r="AX309" s="14"/>
+      <c r="BD309" s="14"/>
+      <c r="BF309" s="14"/>
+      <c r="BG309" s="14"/>
+    </row>
+    <row r="310" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU310" s="14"/>
+      <c r="AX310" s="14"/>
+      <c r="BD310" s="14"/>
+      <c r="BG310" s="14"/>
+    </row>
+    <row r="311" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU311" s="14"/>
+      <c r="AX311" s="14"/>
+      <c r="BD311" s="14"/>
+      <c r="BG311" s="14"/>
+    </row>
+    <row r="312" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU312" s="14"/>
+      <c r="AX312" s="14"/>
+      <c r="BD312" s="14"/>
+      <c r="BG312" s="14"/>
+    </row>
+    <row r="313" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU313" s="14"/>
+      <c r="AX313" s="14"/>
+      <c r="BD313" s="14"/>
+      <c r="BG313" s="14"/>
+    </row>
+    <row r="314" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU314" s="14"/>
+      <c r="AX314" s="14"/>
+      <c r="BD314" s="14"/>
+      <c r="BG314" s="14"/>
+    </row>
+    <row r="315" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU315" s="14"/>
+      <c r="AX315" s="14"/>
+      <c r="BD315" s="14"/>
+      <c r="BG315" s="14"/>
+    </row>
+    <row r="316" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU316" s="14"/>
+      <c r="AX316" s="14"/>
+      <c r="BD316" s="14"/>
+      <c r="BG316" s="14"/>
+    </row>
+    <row r="317" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU317" s="14"/>
+      <c r="AX317" s="14"/>
+      <c r="BD317" s="14"/>
+      <c r="BG317" s="14"/>
+    </row>
+    <row r="318" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU318" s="14"/>
+      <c r="AX318" s="14"/>
+      <c r="BD318" s="14"/>
+      <c r="BG318" s="14"/>
+    </row>
+    <row r="319" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU319" s="14"/>
+      <c r="AX319" s="14"/>
+      <c r="BD319" s="14"/>
+      <c r="BG319" s="14"/>
+    </row>
+    <row r="320" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU320" s="14"/>
+      <c r="AX320" s="14"/>
+      <c r="BD320" s="14"/>
+      <c r="BG320" s="14"/>
+    </row>
+    <row r="321" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU321" s="14"/>
+      <c r="AX321" s="14"/>
+      <c r="BD321" s="14"/>
+      <c r="BG321" s="14"/>
+    </row>
+    <row r="322" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU322" s="14"/>
+      <c r="AX322" s="14"/>
+      <c r="BD322" s="14"/>
+      <c r="BG322" s="14"/>
+    </row>
+    <row r="323" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU323" s="14"/>
+      <c r="AX323" s="14"/>
+      <c r="BD323" s="14"/>
+      <c r="BG323" s="14"/>
+    </row>
+    <row r="324" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU324" s="14"/>
+      <c r="AW324" s="14"/>
+      <c r="AX324" s="14"/>
+      <c r="BD324" s="14"/>
+      <c r="BF324" s="14"/>
+      <c r="BG324" s="14"/>
+    </row>
+    <row r="325" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU325" s="14"/>
+      <c r="AX325" s="14"/>
+      <c r="BD325" s="14"/>
+      <c r="BG325" s="14"/>
+    </row>
+    <row r="326" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU326" s="14"/>
+      <c r="AX326" s="14"/>
+      <c r="BD326" s="14"/>
+      <c r="BG326" s="14"/>
+    </row>
+    <row r="327" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU327" s="14"/>
+      <c r="AX327" s="14"/>
+      <c r="BD327" s="14"/>
+      <c r="BG327" s="14"/>
+    </row>
+    <row r="328" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU328" s="14"/>
+      <c r="AW328" s="14"/>
+      <c r="AX328" s="14"/>
+      <c r="BD328" s="14"/>
+      <c r="BF328" s="14"/>
+      <c r="BG328" s="14"/>
+    </row>
+    <row r="329" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU329" s="14"/>
+      <c r="AX329" s="14"/>
+      <c r="BD329" s="14"/>
+      <c r="BG329" s="14"/>
+    </row>
+    <row r="330" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU330" s="14"/>
+      <c r="AX330" s="14"/>
+      <c r="BD330" s="14"/>
+      <c r="BG330" s="14"/>
+    </row>
+    <row r="331" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU331" s="14"/>
+      <c r="AX331" s="14"/>
+      <c r="BD331" s="14"/>
+      <c r="BG331" s="14"/>
+    </row>
+    <row r="332" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU332" s="14"/>
+      <c r="AX332" s="14"/>
+      <c r="BD332" s="14"/>
+      <c r="BG332" s="14"/>
+    </row>
+    <row r="333" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU333" s="14"/>
+      <c r="AW333" s="14"/>
+      <c r="AX333" s="14"/>
+      <c r="BD333" s="14"/>
+      <c r="BF333" s="14"/>
+      <c r="BG333" s="14"/>
+    </row>
+    <row r="334" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU334" s="14"/>
+      <c r="AW334" s="14"/>
+      <c r="AX334" s="14"/>
+      <c r="BD334" s="14"/>
+      <c r="BF334" s="14"/>
+      <c r="BG334" s="14"/>
+    </row>
+    <row r="335" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU335" s="14"/>
+      <c r="AX335" s="14"/>
+      <c r="BD335" s="14"/>
+      <c r="BG335" s="14"/>
+    </row>
+    <row r="336" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU336" s="14"/>
+      <c r="AX336" s="14"/>
+      <c r="BD336" s="14"/>
+      <c r="BG336" s="14"/>
+    </row>
+    <row r="337" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU337" s="14"/>
+      <c r="AW337" s="14"/>
+      <c r="AX337" s="14"/>
+      <c r="BD337" s="14"/>
+      <c r="BF337" s="14"/>
+      <c r="BG337" s="14"/>
+    </row>
+    <row r="338" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU338" s="14"/>
+      <c r="AX338" s="14"/>
+      <c r="BD338" s="14"/>
+      <c r="BG338" s="14"/>
+    </row>
+    <row r="339" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU339" s="14"/>
+      <c r="AW339" s="14"/>
+      <c r="AX339" s="14"/>
+      <c r="BD339" s="14"/>
+      <c r="BF339" s="14"/>
+      <c r="BG339" s="14"/>
+    </row>
+    <row r="340" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU340" s="14"/>
+      <c r="AX340" s="14"/>
+      <c r="BD340" s="14"/>
+      <c r="BG340" s="14"/>
+    </row>
+    <row r="341" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU341" s="14"/>
+      <c r="AX341" s="14"/>
+      <c r="BD341" s="14"/>
+      <c r="BG341" s="14"/>
+    </row>
+    <row r="342" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU342" s="14"/>
+      <c r="AX342" s="14"/>
+      <c r="BD342" s="14"/>
+      <c r="BG342" s="14"/>
+    </row>
+    <row r="343" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU343" s="14"/>
+      <c r="AW343" s="14"/>
+      <c r="AX343" s="14"/>
+      <c r="BD343" s="14"/>
+      <c r="BF343" s="14"/>
+      <c r="BG343" s="14"/>
+    </row>
+    <row r="344" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU344" s="14"/>
+      <c r="AW344" s="14"/>
+      <c r="AX344" s="14"/>
+      <c r="BD344" s="14"/>
+      <c r="BF344" s="14"/>
+      <c r="BG344" s="14"/>
+    </row>
+    <row r="345" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU345" s="14"/>
+      <c r="AW345" s="14"/>
+      <c r="AX345" s="14"/>
+      <c r="BD345" s="14"/>
+      <c r="BF345" s="14"/>
+      <c r="BG345" s="14"/>
+    </row>
+    <row r="346" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU346" s="14"/>
+      <c r="AW346" s="14"/>
+      <c r="AX346" s="14"/>
+      <c r="BD346" s="14"/>
+      <c r="BF346" s="14"/>
+      <c r="BG346" s="14"/>
+    </row>
+    <row r="347" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU347" s="14"/>
+      <c r="AW347" s="14"/>
+      <c r="AX347" s="14"/>
+      <c r="BD347" s="14"/>
+      <c r="BF347" s="14"/>
+      <c r="BG347" s="14"/>
+    </row>
+    <row r="348" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU348" s="14"/>
+      <c r="AX348" s="14"/>
+      <c r="BD348" s="14"/>
+      <c r="BG348" s="14"/>
+    </row>
+    <row r="349" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU349" s="14"/>
+      <c r="AW349" s="14"/>
+      <c r="AX349" s="14"/>
+      <c r="BD349" s="14"/>
+      <c r="BF349" s="14"/>
+      <c r="BG349" s="14"/>
+    </row>
+    <row r="350" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU350" s="14"/>
+      <c r="AX350" s="14"/>
+      <c r="BD350" s="14"/>
+      <c r="BG350" s="14"/>
+    </row>
+    <row r="351" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU351" s="14"/>
+      <c r="AX351" s="14"/>
+      <c r="BD351" s="14"/>
+      <c r="BG351" s="14"/>
+    </row>
+    <row r="352" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU352" s="14"/>
+      <c r="AX352" s="14"/>
+      <c r="BD352" s="14"/>
+      <c r="BG352" s="14"/>
+    </row>
+    <row r="353" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU353" s="14"/>
+      <c r="AW353" s="14"/>
+      <c r="AX353" s="14"/>
+      <c r="BD353" s="14"/>
+      <c r="BF353" s="14"/>
+      <c r="BG353" s="14"/>
+    </row>
+    <row r="354" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU354" s="14"/>
+      <c r="AX354" s="14"/>
+      <c r="BD354" s="14"/>
+      <c r="BG354" s="14"/>
+    </row>
+    <row r="355" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU355" s="14"/>
+      <c r="AX355" s="14"/>
+      <c r="BD355" s="14"/>
+      <c r="BG355" s="14"/>
+    </row>
+    <row r="356" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU356" s="14"/>
+      <c r="AX356" s="14"/>
+      <c r="BD356" s="14"/>
+      <c r="BG356" s="14"/>
+    </row>
+    <row r="357" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU357" s="14"/>
+      <c r="AX357" s="14"/>
+      <c r="BD357" s="14"/>
+      <c r="BG357" s="14"/>
+    </row>
+    <row r="358" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU358" s="14"/>
+      <c r="AX358" s="14"/>
+      <c r="BD358" s="14"/>
+      <c r="BG358" s="14"/>
+    </row>
+    <row r="359" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU359" s="14"/>
+      <c r="AW359" s="14"/>
+      <c r="AX359" s="14"/>
+      <c r="BD359" s="14"/>
+      <c r="BF359" s="14"/>
+      <c r="BG359" s="14"/>
+    </row>
+    <row r="360" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU360" s="14"/>
+      <c r="AX360" s="14"/>
+      <c r="BD360" s="14"/>
+      <c r="BG360" s="14"/>
+    </row>
+    <row r="361" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU361" s="14"/>
+      <c r="AX361" s="14"/>
+      <c r="BD361" s="14"/>
+      <c r="BG361" s="14"/>
+    </row>
+    <row r="362" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU362" s="14"/>
+      <c r="AW362" s="14"/>
+      <c r="AX362" s="14"/>
+      <c r="BD362" s="14"/>
+      <c r="BF362" s="14"/>
+      <c r="BG362" s="14"/>
+    </row>
+    <row r="363" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU363" s="14"/>
+      <c r="AX363" s="14"/>
+      <c r="BD363" s="14"/>
+      <c r="BG363" s="14"/>
+    </row>
+    <row r="364" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU364" s="14"/>
+      <c r="AX364" s="14"/>
+      <c r="BD364" s="14"/>
+      <c r="BF364" s="14"/>
+      <c r="BG364" s="14"/>
+    </row>
+    <row r="365" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU365" s="14"/>
+      <c r="AX365" s="14"/>
+      <c r="BD365" s="14"/>
+      <c r="BF365" s="14"/>
+      <c r="BG365" s="14"/>
+    </row>
+    <row r="366" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU366" s="14"/>
+      <c r="AX366" s="14"/>
+      <c r="BD366" s="14"/>
+      <c r="BG366" s="14"/>
+    </row>
+    <row r="367" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU367" s="14"/>
+      <c r="AW367" s="14"/>
+      <c r="AX367" s="14"/>
+      <c r="BD367" s="14"/>
+      <c r="BF367" s="14"/>
+      <c r="BG367" s="14"/>
+    </row>
+    <row r="368" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU368" s="14"/>
+      <c r="AX368" s="14"/>
+      <c r="BD368" s="14"/>
+      <c r="BG368" s="14"/>
+    </row>
+    <row r="369" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU369" s="14"/>
+      <c r="AX369" s="14"/>
+      <c r="BD369" s="14"/>
+      <c r="BG369" s="14"/>
+    </row>
+    <row r="370" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU370" s="14"/>
+      <c r="AX370" s="14"/>
+      <c r="BD370" s="14"/>
+      <c r="BG370" s="14"/>
+    </row>
+    <row r="371" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU371" s="14"/>
+      <c r="AX371" s="14"/>
+      <c r="BD371" s="14"/>
+      <c r="BG371" s="14"/>
+    </row>
+    <row r="372" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU372" s="14"/>
+      <c r="AX372" s="14"/>
+      <c r="BD372" s="14"/>
+      <c r="BG372" s="14"/>
+    </row>
+    <row r="373" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU373" s="14"/>
+      <c r="AX373" s="14"/>
+      <c r="BD373" s="14"/>
+      <c r="BG373" s="14"/>
+    </row>
+    <row r="374" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU374" s="14"/>
+      <c r="AX374" s="14"/>
+      <c r="BD374" s="14"/>
+      <c r="BG374" s="14"/>
+    </row>
+    <row r="375" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU375" s="14"/>
+      <c r="AW375" s="14"/>
+      <c r="AX375" s="14"/>
+      <c r="BD375" s="14"/>
+      <c r="BF375" s="14"/>
+      <c r="BG375" s="14"/>
+    </row>
+    <row r="376" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU376" s="14"/>
+      <c r="AX376" s="14"/>
+      <c r="BD376" s="14"/>
+      <c r="BG376" s="14"/>
+    </row>
+    <row r="377" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU377" s="14"/>
+      <c r="AW377" s="14"/>
+      <c r="AX377" s="14"/>
+      <c r="BD377" s="14"/>
+      <c r="BF377" s="14"/>
+      <c r="BG377" s="14"/>
+    </row>
+    <row r="378" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU378" s="14"/>
+      <c r="AX378" s="14"/>
+      <c r="BD378" s="14"/>
+      <c r="BG378" s="14"/>
+    </row>
+    <row r="379" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU379" s="14"/>
+      <c r="AX379" s="14"/>
+      <c r="BD379" s="14"/>
+      <c r="BG379" s="14"/>
+    </row>
+    <row r="380" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU380" s="14"/>
+      <c r="AX380" s="14"/>
+      <c r="BD380" s="14"/>
+      <c r="BG380" s="14"/>
+    </row>
+    <row r="381" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU381" s="14"/>
+      <c r="AW381" s="14"/>
+      <c r="AX381" s="14"/>
+      <c r="BD381" s="14"/>
+      <c r="BF381" s="14"/>
+      <c r="BG381" s="14"/>
+    </row>
+    <row r="382" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU382" s="14"/>
+      <c r="AX382" s="14"/>
+      <c r="BD382" s="14"/>
+      <c r="BG382" s="14"/>
+    </row>
+    <row r="383" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU383" s="14"/>
+      <c r="AX383" s="14"/>
+      <c r="BD383" s="14"/>
+      <c r="BG383" s="14"/>
+    </row>
+    <row r="384" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU384" s="14"/>
+      <c r="AW384" s="14"/>
+      <c r="AX384" s="14"/>
+      <c r="BD384" s="14"/>
+      <c r="BF384" s="14"/>
+      <c r="BG384" s="14"/>
+    </row>
+    <row r="385" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU385" s="14"/>
+      <c r="AW385" s="14"/>
+      <c r="AX385" s="14"/>
+      <c r="BD385" s="14"/>
+      <c r="BF385" s="14"/>
+      <c r="BG385" s="14"/>
+    </row>
+    <row r="386" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU386" s="14"/>
+      <c r="AX386" s="14"/>
+      <c r="BD386" s="14"/>
+      <c r="BG386" s="14"/>
+    </row>
+    <row r="387" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU387" s="14"/>
+      <c r="AX387" s="14"/>
+      <c r="BD387" s="14"/>
+      <c r="BG387" s="14"/>
+    </row>
+    <row r="388" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU388" s="14"/>
+      <c r="AW388" s="14"/>
+      <c r="AX388" s="14"/>
+      <c r="BD388" s="14"/>
+      <c r="BF388" s="14"/>
+      <c r="BG388" s="14"/>
+    </row>
+    <row r="389" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU389" s="14"/>
+      <c r="AX389" s="14"/>
+      <c r="BD389" s="14"/>
+      <c r="BG389" s="14"/>
+    </row>
+    <row r="390" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU390" s="14"/>
+      <c r="AX390" s="14"/>
+      <c r="BD390" s="14"/>
+      <c r="BG390" s="14"/>
+    </row>
+    <row r="391" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU391" s="14"/>
+      <c r="AX391" s="14"/>
+      <c r="BD391" s="14"/>
+      <c r="BG391" s="14"/>
+    </row>
+    <row r="392" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU392" s="14"/>
+      <c r="AW392" s="14"/>
+      <c r="AX392" s="14"/>
+      <c r="BD392" s="14"/>
+      <c r="BF392" s="14"/>
+      <c r="BG392" s="14"/>
+    </row>
+    <row r="393" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU393" s="14"/>
+      <c r="AW393" s="14"/>
+      <c r="AX393" s="14"/>
+      <c r="BD393" s="14"/>
+      <c r="BF393" s="14"/>
+      <c r="BG393" s="14"/>
+    </row>
+    <row r="394" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU394" s="14"/>
+      <c r="AW394" s="14"/>
+      <c r="AX394" s="14"/>
+      <c r="BD394" s="14"/>
+      <c r="BF394" s="14"/>
+      <c r="BG394" s="14"/>
+    </row>
+    <row r="395" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU395" s="14"/>
+      <c r="AX395" s="14"/>
+      <c r="BD395" s="14"/>
+      <c r="BG395" s="14"/>
+    </row>
+    <row r="396" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU396" s="14"/>
+      <c r="AX396" s="14"/>
+      <c r="BD396" s="14"/>
+      <c r="BF396" s="14"/>
+      <c r="BG396" s="14"/>
+    </row>
+    <row r="397" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU397" s="14"/>
+      <c r="AX397" s="14"/>
+      <c r="BD397" s="14"/>
+      <c r="BF397" s="14"/>
+      <c r="BG397" s="14"/>
+    </row>
+    <row r="398" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU398" s="14"/>
+      <c r="AX398" s="14"/>
+      <c r="BD398" s="14"/>
+      <c r="BG398" s="14"/>
+    </row>
+    <row r="399" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU399" s="14"/>
+      <c r="AW399" s="14"/>
+      <c r="AX399" s="14"/>
+      <c r="BD399" s="14"/>
+      <c r="BF399" s="14"/>
+      <c r="BG399" s="14"/>
+    </row>
+    <row r="400" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU400" s="14"/>
+      <c r="AX400" s="14"/>
+      <c r="BD400" s="14"/>
+      <c r="BF400" s="14"/>
+      <c r="BG400" s="14"/>
+    </row>
+    <row r="401" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU401" s="14"/>
+      <c r="AX401" s="14"/>
+      <c r="BD401" s="14"/>
+      <c r="BF401" s="14"/>
+      <c r="BG401" s="14"/>
+    </row>
+    <row r="402" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU402" s="14"/>
+      <c r="AX402" s="14"/>
+      <c r="BD402" s="14"/>
+      <c r="BG402" s="14"/>
+    </row>
+    <row r="403" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU403" s="14"/>
+      <c r="AX403" s="14"/>
+      <c r="BD403" s="14"/>
+      <c r="BF403" s="14"/>
+      <c r="BG403" s="14"/>
+    </row>
+    <row r="404" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU404" s="14"/>
+      <c r="AW404" s="14"/>
+      <c r="AX404" s="14"/>
+      <c r="BD404" s="14"/>
+      <c r="BF404" s="14"/>
+      <c r="BG404" s="14"/>
+    </row>
+    <row r="405" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU405" s="14"/>
+      <c r="AW405" s="14"/>
+      <c r="AX405" s="14"/>
+      <c r="BD405" s="14"/>
+      <c r="BF405" s="14"/>
+      <c r="BG405" s="14"/>
+    </row>
+    <row r="406" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU406" s="14"/>
+      <c r="AW406" s="14"/>
+      <c r="AX406" s="14"/>
+      <c r="BD406" s="14"/>
+      <c r="BF406" s="14"/>
+      <c r="BG406" s="14"/>
+    </row>
+    <row r="407" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU407" s="14"/>
+      <c r="AX407" s="14"/>
+      <c r="BD407" s="14"/>
+      <c r="BG407" s="14"/>
+    </row>
+    <row r="408" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU408" s="14"/>
+      <c r="AW408" s="14"/>
+      <c r="AX408" s="14"/>
+      <c r="BD408" s="14"/>
+      <c r="BF408" s="14"/>
+      <c r="BG408" s="14"/>
+    </row>
+    <row r="409" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU409" s="14"/>
+      <c r="AX409" s="14"/>
+      <c r="BD409" s="14"/>
+      <c r="BG409" s="14"/>
+    </row>
+    <row r="410" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU410" s="14"/>
+      <c r="AW410" s="14"/>
+      <c r="AX410" s="14"/>
+      <c r="BD410" s="14"/>
+      <c r="BF410" s="14"/>
+      <c r="BG410" s="14"/>
+    </row>
+    <row r="411" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU411" s="14"/>
+      <c r="AX411" s="14"/>
+      <c r="BD411" s="14"/>
+      <c r="BG411" s="14"/>
+    </row>
+    <row r="412" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU412" s="14"/>
+      <c r="AX412" s="14"/>
+      <c r="BD412" s="14"/>
+      <c r="BG412" s="14"/>
+    </row>
+    <row r="413" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU413" s="14"/>
+      <c r="AX413" s="14"/>
+      <c r="BD413" s="14"/>
+      <c r="BG413" s="14"/>
+    </row>
+    <row r="414" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU414" s="14"/>
+      <c r="AX414" s="14"/>
+      <c r="BD414" s="14"/>
+      <c r="BG414" s="14"/>
+    </row>
+    <row r="415" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU415" s="14"/>
+      <c r="AW415" s="14"/>
+      <c r="AX415" s="14"/>
+      <c r="BD415" s="14"/>
+      <c r="BF415" s="14"/>
+      <c r="BG415" s="14"/>
+    </row>
+    <row r="416" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU416" s="14"/>
+      <c r="AX416" s="14"/>
+      <c r="BD416" s="14"/>
+      <c r="BG416" s="14"/>
+    </row>
+    <row r="417" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU417" s="14"/>
+      <c r="AX417" s="14"/>
+      <c r="BD417" s="14"/>
+      <c r="BG417" s="14"/>
+    </row>
+    <row r="418" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU418" s="14"/>
+      <c r="AX418" s="14"/>
+      <c r="BD418" s="14"/>
+      <c r="BG418" s="14"/>
+    </row>
+    <row r="419" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU419" s="14"/>
+      <c r="AX419" s="14"/>
+      <c r="BD419" s="14"/>
+      <c r="BG419" s="14"/>
+    </row>
+    <row r="420" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU420" s="14"/>
+      <c r="AX420" s="14"/>
+      <c r="BD420" s="14"/>
+      <c r="BF420" s="14"/>
+      <c r="BG420" s="14"/>
+    </row>
+    <row r="421" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU421" s="14"/>
+      <c r="AX421" s="14"/>
+      <c r="BD421" s="14"/>
+      <c r="BF421" s="14"/>
+      <c r="BG421" s="14"/>
+    </row>
+    <row r="422" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU422" s="14"/>
+      <c r="AX422" s="14"/>
+      <c r="BD422" s="14"/>
+      <c r="BF422" s="14"/>
+      <c r="BG422" s="14"/>
+    </row>
+    <row r="423" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU423" s="14"/>
+      <c r="AW423" s="14"/>
+      <c r="AX423" s="14"/>
+      <c r="BD423" s="14"/>
+      <c r="BF423" s="14"/>
+      <c r="BG423" s="14"/>
+    </row>
+    <row r="424" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU424" s="14"/>
+      <c r="AW424" s="14"/>
+      <c r="AX424" s="14"/>
+      <c r="BD424" s="14"/>
+      <c r="BF424" s="14"/>
+      <c r="BG424" s="14"/>
+    </row>
+    <row r="425" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU425" s="14"/>
+      <c r="AX425" s="14"/>
+      <c r="BD425" s="14"/>
+      <c r="BG425" s="14"/>
+    </row>
+    <row r="426" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU426" s="14"/>
+      <c r="AX426" s="14"/>
+      <c r="BD426" s="14"/>
+      <c r="BF426" s="14"/>
+      <c r="BG426" s="14"/>
+    </row>
+    <row r="427" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU427" s="14"/>
+      <c r="AX427" s="14"/>
+      <c r="BD427" s="14"/>
+      <c r="BG427" s="14"/>
+    </row>
+    <row r="428" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU428" s="14"/>
+      <c r="AX428" s="14"/>
+      <c r="BD428" s="14"/>
+      <c r="BG428" s="14"/>
+    </row>
+    <row r="429" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU429" s="14"/>
+      <c r="AX429" s="14"/>
+      <c r="BD429" s="14"/>
+      <c r="BG429" s="14"/>
+    </row>
+    <row r="430" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU430" s="14"/>
+      <c r="AX430" s="14"/>
+      <c r="BD430" s="14"/>
+      <c r="BG430" s="14"/>
+    </row>
+    <row r="431" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU431" s="14"/>
+      <c r="AX431" s="14"/>
+      <c r="BD431" s="14"/>
+      <c r="BG431" s="14"/>
+    </row>
+    <row r="432" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU432" s="14"/>
+      <c r="AX432" s="14"/>
+      <c r="BD432" s="14"/>
+      <c r="BG432" s="14"/>
+    </row>
+    <row r="433" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU433" s="14"/>
+      <c r="AX433" s="14"/>
+      <c r="BD433" s="14"/>
+      <c r="BG433" s="14"/>
+    </row>
+    <row r="434" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU434" s="14"/>
+      <c r="AW434" s="14"/>
+      <c r="AX434" s="14"/>
+      <c r="BD434" s="14"/>
+      <c r="BF434" s="14"/>
+      <c r="BG434" s="14"/>
+    </row>
+    <row r="435" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU435" s="14"/>
+      <c r="AX435" s="14"/>
+      <c r="BD435" s="14"/>
+      <c r="BG435" s="14"/>
+    </row>
+    <row r="436" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU436" s="14"/>
+      <c r="AW436" s="14"/>
+      <c r="AX436" s="14"/>
+      <c r="BD436" s="14"/>
+      <c r="BF436" s="14"/>
+      <c r="BG436" s="14"/>
+    </row>
+    <row r="437" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU437" s="14"/>
+      <c r="AW437" s="14"/>
+      <c r="AX437" s="14"/>
+      <c r="BD437" s="14"/>
+      <c r="BF437" s="14"/>
+      <c r="BG437" s="14"/>
+    </row>
+    <row r="438" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU438" s="14"/>
+      <c r="AW438" s="14"/>
+      <c r="AX438" s="14"/>
+      <c r="BD438" s="14"/>
+      <c r="BF438" s="14"/>
+      <c r="BG438" s="14"/>
+    </row>
+    <row r="439" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU439" s="14"/>
+      <c r="AW439" s="14"/>
+      <c r="AX439" s="14"/>
+      <c r="BD439" s="14"/>
+      <c r="BF439" s="14"/>
+      <c r="BG439" s="14"/>
+    </row>
+    <row r="440" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU440" s="14"/>
+      <c r="AX440" s="14"/>
+      <c r="BD440" s="14"/>
+      <c r="BG440" s="14"/>
+    </row>
+    <row r="441" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU441" s="14"/>
+      <c r="AX441" s="14"/>
+      <c r="BD441" s="14"/>
+      <c r="BG441" s="14"/>
+    </row>
+    <row r="442" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU442" s="14"/>
+      <c r="AX442" s="14"/>
+      <c r="BD442" s="14"/>
+      <c r="BG442" s="14"/>
+    </row>
+    <row r="443" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU443" s="14"/>
+      <c r="AX443" s="14"/>
+      <c r="BD443" s="14"/>
+      <c r="BG443" s="14"/>
+    </row>
+    <row r="444" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU444" s="14"/>
+      <c r="AX444" s="14"/>
+      <c r="BD444" s="14"/>
+      <c r="BG444" s="14"/>
+    </row>
+    <row r="445" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU445" s="14"/>
+      <c r="AX445" s="14"/>
+      <c r="BD445" s="14"/>
+      <c r="BF445" s="14"/>
+      <c r="BG445" s="14"/>
+    </row>
+    <row r="446" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU446" s="14"/>
+      <c r="AX446" s="14"/>
+      <c r="BD446" s="14"/>
+      <c r="BG446" s="14"/>
+    </row>
+    <row r="447" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU447" s="14"/>
+      <c r="AX447" s="14"/>
+      <c r="BD447" s="14"/>
+      <c r="BG447" s="14"/>
+    </row>
+    <row r="448" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU448" s="14"/>
+      <c r="AX448" s="14"/>
+      <c r="BD448" s="14"/>
+      <c r="BG448" s="14"/>
+    </row>
+    <row r="449" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU449" s="14"/>
+      <c r="AX449" s="14"/>
+      <c r="BD449" s="14"/>
+      <c r="BG449" s="14"/>
+    </row>
+    <row r="450" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU450" s="14"/>
+      <c r="AW450" s="14"/>
+      <c r="AX450" s="14"/>
+      <c r="BD450" s="14"/>
+      <c r="BF450" s="14"/>
+      <c r="BG450" s="14"/>
+    </row>
+    <row r="451" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU451" s="14"/>
+      <c r="AW451" s="14"/>
+      <c r="AX451" s="14"/>
+      <c r="BD451" s="14"/>
+      <c r="BF451" s="14"/>
+      <c r="BG451" s="14"/>
+    </row>
+    <row r="452" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU452" s="14"/>
+      <c r="AX452" s="14"/>
+      <c r="BD452" s="14"/>
+      <c r="BG452" s="14"/>
+    </row>
+    <row r="453" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU453" s="14"/>
+      <c r="AX453" s="14"/>
+      <c r="BD453" s="14"/>
+      <c r="BG453" s="14"/>
+    </row>
+    <row r="454" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU454" s="14"/>
+      <c r="AX454" s="14"/>
+      <c r="BD454" s="14"/>
+      <c r="BF454" s="14"/>
+      <c r="BG454" s="14"/>
+    </row>
+    <row r="455" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU455" s="14"/>
+      <c r="AX455" s="14"/>
+      <c r="BD455" s="14"/>
+      <c r="BF455" s="14"/>
+      <c r="BG455" s="14"/>
+    </row>
+    <row r="456" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU456" s="14"/>
+      <c r="AX456" s="14"/>
+      <c r="BD456" s="14"/>
+      <c r="BF456" s="14"/>
+      <c r="BG456" s="14"/>
+    </row>
+    <row r="457" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU457" s="14"/>
+      <c r="AX457" s="14"/>
+      <c r="BD457" s="14"/>
+      <c r="BF457" s="14"/>
+      <c r="BG457" s="14"/>
+    </row>
+    <row r="458" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU458" s="14"/>
+      <c r="AX458" s="14"/>
+      <c r="BD458" s="14"/>
+      <c r="BF458" s="14"/>
+      <c r="BG458" s="14"/>
+    </row>
+    <row r="459" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU459" s="14"/>
+      <c r="AW459" s="14"/>
+      <c r="AX459" s="14"/>
+      <c r="BD459" s="14"/>
+      <c r="BF459" s="14"/>
+      <c r="BG459" s="14"/>
+    </row>
+    <row r="460" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU460" s="14"/>
+      <c r="AW460" s="14"/>
+      <c r="AX460" s="14"/>
+      <c r="BD460" s="14"/>
+      <c r="BF460" s="14"/>
+      <c r="BG460" s="14"/>
+    </row>
+    <row r="461" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU461" s="14"/>
+      <c r="AW461" s="14"/>
+      <c r="AX461" s="14"/>
+      <c r="BD461" s="14"/>
+      <c r="BF461" s="14"/>
+      <c r="BG461" s="14"/>
+    </row>
+    <row r="462" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU462" s="14"/>
+      <c r="AW462" s="14"/>
+      <c r="AX462" s="14"/>
+      <c r="BD462" s="14"/>
+      <c r="BF462" s="14"/>
+      <c r="BG462" s="14"/>
+    </row>
+    <row r="463" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU463" s="14"/>
+      <c r="AX463" s="14"/>
+      <c r="BD463" s="14"/>
+      <c r="BG463" s="14"/>
+    </row>
+    <row r="464" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU464" s="14"/>
+      <c r="AX464" s="14"/>
+      <c r="BD464" s="14"/>
+      <c r="BF464" s="14"/>
+      <c r="BG464" s="14"/>
+    </row>
+    <row r="465" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU465" s="14"/>
+      <c r="AX465" s="14"/>
+      <c r="BD465" s="14"/>
+      <c r="BF465" s="14"/>
+      <c r="BG465" s="14"/>
+    </row>
+    <row r="466" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU466" s="14"/>
+      <c r="AX466" s="14"/>
+      <c r="BD466" s="14"/>
+      <c r="BF466" s="14"/>
+      <c r="BG466" s="14"/>
+    </row>
+    <row r="467" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU467" s="14"/>
+      <c r="AX467" s="14"/>
+      <c r="BD467" s="14"/>
+      <c r="BF467" s="14"/>
+      <c r="BG467" s="14"/>
+    </row>
+    <row r="468" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU468" s="14"/>
+      <c r="AX468" s="14"/>
+      <c r="BD468" s="14"/>
+      <c r="BG468" s="14"/>
+    </row>
+    <row r="469" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU469" s="14"/>
+      <c r="AX469" s="14"/>
+      <c r="BD469" s="14"/>
+      <c r="BG469" s="14"/>
+    </row>
+    <row r="470" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU470" s="14"/>
+      <c r="AX470" s="14"/>
+      <c r="BD470" s="14"/>
+      <c r="BG470" s="14"/>
+    </row>
+    <row r="471" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU471" s="14"/>
+      <c r="AX471" s="14"/>
+      <c r="BD471" s="14"/>
+      <c r="BG471" s="14"/>
+    </row>
+    <row r="472" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU472" s="14"/>
+      <c r="AX472" s="14"/>
+      <c r="BD472" s="14"/>
+      <c r="BG472" s="14"/>
+    </row>
+    <row r="473" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU473" s="14"/>
+      <c r="AX473" s="14"/>
+      <c r="BD473" s="14"/>
+      <c r="BG473" s="14"/>
+    </row>
+    <row r="474" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU474" s="14"/>
+      <c r="AX474" s="14"/>
+      <c r="BD474" s="14"/>
+      <c r="BG474" s="14"/>
+    </row>
+    <row r="475" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU475" s="14"/>
+      <c r="AX475" s="14"/>
+      <c r="BD475" s="14"/>
+      <c r="BG475" s="14"/>
+    </row>
+    <row r="476" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU476" s="14"/>
+      <c r="AX476" s="14"/>
+      <c r="BD476" s="14"/>
+      <c r="BG476" s="14"/>
+    </row>
+    <row r="477" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU477" s="14"/>
+      <c r="AX477" s="14"/>
+      <c r="BD477" s="14"/>
+      <c r="BG477" s="14"/>
+    </row>
+    <row r="478" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU478" s="14"/>
+      <c r="AX478" s="14"/>
+      <c r="BD478" s="14"/>
+      <c r="BF478" s="14"/>
+      <c r="BG478" s="14"/>
+    </row>
+    <row r="479" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU479" s="14"/>
+      <c r="AX479" s="14"/>
+      <c r="BD479" s="14"/>
+      <c r="BG479" s="14"/>
+    </row>
+    <row r="480" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU480" s="14"/>
+      <c r="AW480" s="14"/>
+      <c r="AX480" s="14"/>
+      <c r="BD480" s="14"/>
+      <c r="BF480" s="14"/>
+      <c r="BG480" s="14"/>
+    </row>
+    <row r="481" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU481" s="14"/>
+      <c r="AX481" s="14"/>
+      <c r="BD481" s="14"/>
+      <c r="BG481" s="14"/>
+    </row>
+    <row r="482" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU482" s="14"/>
+      <c r="AX482" s="14"/>
+      <c r="BD482" s="14"/>
+      <c r="BG482" s="14"/>
+    </row>
+    <row r="483" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU483" s="14"/>
+      <c r="AX483" s="14"/>
+      <c r="BD483" s="14"/>
+      <c r="BG483" s="14"/>
+    </row>
+    <row r="484" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU484" s="14"/>
+      <c r="AX484" s="14"/>
+      <c r="BD484" s="14"/>
+      <c r="BG484" s="14"/>
+    </row>
+    <row r="485" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU485" s="14"/>
+      <c r="AW485" s="14"/>
+      <c r="AX485" s="14"/>
+      <c r="BD485" s="14"/>
+      <c r="BF485" s="14"/>
+      <c r="BG485" s="14"/>
+    </row>
+    <row r="486" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU486" s="14"/>
+      <c r="AW486" s="14"/>
+      <c r="AX486" s="14"/>
+      <c r="BD486" s="14"/>
+      <c r="BF486" s="14"/>
+      <c r="BG486" s="14"/>
+    </row>
+    <row r="487" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU487" s="14"/>
+      <c r="AX487" s="14"/>
+      <c r="BD487" s="14"/>
+      <c r="BG487" s="14"/>
+    </row>
+    <row r="488" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU488" s="14"/>
+      <c r="AX488" s="14"/>
+      <c r="BD488" s="14"/>
+      <c r="BG488" s="14"/>
+    </row>
+    <row r="489" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU489" s="14"/>
+      <c r="AX489" s="14"/>
+      <c r="BD489" s="14"/>
+      <c r="BG489" s="14"/>
+    </row>
+    <row r="490" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU490" s="14"/>
+      <c r="AX490" s="14"/>
+      <c r="BD490" s="14"/>
+      <c r="BG490" s="14"/>
+    </row>
+    <row r="491" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU491" s="14"/>
+      <c r="AX491" s="14"/>
+      <c r="BD491" s="14"/>
+      <c r="BG491" s="14"/>
+    </row>
+    <row r="492" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU492" s="14"/>
+      <c r="AX492" s="14"/>
+      <c r="BD492" s="14"/>
+      <c r="BG492" s="14"/>
+    </row>
+    <row r="493" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU493" s="14"/>
+      <c r="AX493" s="14"/>
+      <c r="BD493" s="14"/>
+      <c r="BG493" s="14"/>
+    </row>
+    <row r="494" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU494" s="14"/>
+      <c r="AX494" s="14"/>
+      <c r="BD494" s="14"/>
+      <c r="BG494" s="14"/>
+    </row>
+    <row r="495" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU495" s="14"/>
+      <c r="AX495" s="14"/>
+      <c r="BD495" s="14"/>
+      <c r="BG495" s="14"/>
+    </row>
+    <row r="496" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU496" s="14"/>
+      <c r="AX496" s="14"/>
+      <c r="BD496" s="14"/>
+      <c r="BG496" s="14"/>
+    </row>
+    <row r="497" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU497" s="14"/>
+      <c r="AX497" s="14"/>
+      <c r="BD497" s="14"/>
+      <c r="BG497" s="14"/>
+    </row>
+    <row r="498" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU498" s="14"/>
+      <c r="AX498" s="14"/>
+      <c r="BD498" s="14"/>
+      <c r="BG498" s="14"/>
+    </row>
+    <row r="499" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU499" s="14"/>
+      <c r="AX499" s="14"/>
+      <c r="BD499" s="14"/>
+      <c r="BG499" s="14"/>
+    </row>
+    <row r="500" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU500" s="14"/>
+      <c r="AX500" s="14"/>
+      <c r="BD500" s="14"/>
+      <c r="BG500" s="14"/>
+    </row>
+    <row r="501" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU501" s="14"/>
+      <c r="AX501" s="14"/>
+      <c r="BD501" s="14"/>
+      <c r="BG501" s="14"/>
+    </row>
+    <row r="502" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU502" s="14"/>
+      <c r="AX502" s="14"/>
+      <c r="BD502" s="14"/>
+      <c r="BG502" s="14"/>
+    </row>
+    <row r="503" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU503" s="14"/>
+      <c r="AX503" s="14"/>
+      <c r="BD503" s="14"/>
+      <c r="BG503" s="14"/>
+    </row>
+    <row r="504" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU504" s="14"/>
+      <c r="AX504" s="14"/>
+      <c r="BD504" s="14"/>
+      <c r="BG504" s="14"/>
+    </row>
+    <row r="505" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU505" s="14"/>
+      <c r="AX505" s="14"/>
+      <c r="BD505" s="14"/>
+      <c r="BG505" s="14"/>
+    </row>
+    <row r="506" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU506" s="14"/>
+      <c r="AX506" s="14"/>
+      <c r="BD506" s="14"/>
+      <c r="BG506" s="14"/>
+    </row>
+    <row r="507" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU507" s="14"/>
+      <c r="AX507" s="14"/>
+      <c r="BD507" s="14"/>
+      <c r="BG507" s="14"/>
+    </row>
+    <row r="508" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU508" s="14"/>
+      <c r="AX508" s="14"/>
+      <c r="BD508" s="14"/>
+      <c r="BG508" s="14"/>
+    </row>
+    <row r="509" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU509" s="14"/>
+      <c r="AX509" s="14"/>
+      <c r="BD509" s="14"/>
+      <c r="BG509" s="14"/>
+    </row>
+    <row r="510" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU510" s="14"/>
+      <c r="AX510" s="14"/>
+      <c r="BD510" s="14"/>
+      <c r="BG510" s="14"/>
+    </row>
+    <row r="511" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU511" s="14"/>
+      <c r="AX511" s="14"/>
+      <c r="BD511" s="14"/>
+      <c r="BG511" s="14"/>
+    </row>
+    <row r="512" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU512" s="14"/>
+      <c r="AX512" s="14"/>
+      <c r="BD512" s="14"/>
+      <c r="BG512" s="14"/>
+    </row>
+    <row r="513" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU513" s="14"/>
+      <c r="AX513" s="14"/>
+      <c r="BD513" s="14"/>
+      <c r="BG513" s="14"/>
+    </row>
+    <row r="514" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU514" s="14"/>
+      <c r="AX514" s="14"/>
+      <c r="BD514" s="14"/>
+      <c r="BG514" s="14"/>
+    </row>
+    <row r="515" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU515" s="14"/>
+      <c r="AX515" s="14"/>
+      <c r="BD515" s="14"/>
+      <c r="BG515" s="14"/>
+    </row>
+    <row r="516" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU516" s="14"/>
+      <c r="AX516" s="14"/>
+      <c r="BD516" s="14"/>
+      <c r="BG516" s="14"/>
+    </row>
+    <row r="517" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU517" s="14"/>
+      <c r="AX517" s="14"/>
+      <c r="BD517" s="14"/>
+      <c r="BG517" s="14"/>
+    </row>
+    <row r="518" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU518" s="14"/>
+      <c r="AX518" s="14"/>
+      <c r="BD518" s="14"/>
+      <c r="BG518" s="14"/>
+    </row>
+    <row r="519" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU519" s="14"/>
+      <c r="AX519" s="14"/>
+      <c r="BD519" s="14"/>
+      <c r="BG519" s="14"/>
+    </row>
+    <row r="520" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU520" s="14"/>
+      <c r="AX520" s="14"/>
+      <c r="BD520" s="14"/>
+      <c r="BG520" s="14"/>
+    </row>
+    <row r="521" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU521" s="14"/>
+      <c r="AX521" s="14"/>
+      <c r="BD521" s="14"/>
+      <c r="BG521" s="14"/>
+    </row>
+    <row r="522" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU522" s="14"/>
+      <c r="AX522" s="14"/>
+      <c r="BD522" s="14"/>
+      <c r="BG522" s="14"/>
+    </row>
+    <row r="523" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU523" s="14"/>
+      <c r="AX523" s="14"/>
+      <c r="BD523" s="14"/>
+      <c r="BG523" s="14"/>
+    </row>
+    <row r="524" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU524" s="14"/>
+      <c r="AW524" s="14"/>
+      <c r="AX524" s="14"/>
+      <c r="BD524" s="14"/>
+      <c r="BF524" s="14"/>
+      <c r="BG524" s="14"/>
+    </row>
+    <row r="525" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU525" s="14"/>
+      <c r="AX525" s="14"/>
+      <c r="BD525" s="14"/>
+      <c r="BG525" s="14"/>
+    </row>
+    <row r="526" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU526" s="14"/>
+      <c r="AX526" s="14"/>
+      <c r="BD526" s="14"/>
+      <c r="BG526" s="14"/>
+    </row>
+    <row r="527" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU527" s="14"/>
+      <c r="AX527" s="14"/>
+      <c r="BD527" s="14"/>
+      <c r="BG527" s="14"/>
+    </row>
+    <row r="528" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU528" s="14"/>
+      <c r="AW528" s="14"/>
+      <c r="AX528" s="14"/>
+      <c r="BD528" s="14"/>
+      <c r="BF528" s="14"/>
+      <c r="BG528" s="14"/>
+    </row>
+    <row r="529" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU529" s="14"/>
+      <c r="AW529" s="14"/>
+      <c r="AX529" s="14"/>
+      <c r="BD529" s="14"/>
+      <c r="BF529" s="14"/>
+      <c r="BG529" s="14"/>
+    </row>
+    <row r="530" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU530" s="14"/>
+      <c r="AW530" s="14"/>
+      <c r="AX530" s="14"/>
+      <c r="BD530" s="14"/>
+      <c r="BF530" s="14"/>
+      <c r="BG530" s="14"/>
+    </row>
+    <row r="531" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU531" s="14"/>
+      <c r="AX531" s="14"/>
+      <c r="BD531" s="14"/>
+      <c r="BG531" s="14"/>
+    </row>
+    <row r="532" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU532" s="14"/>
+      <c r="AX532" s="14"/>
+      <c r="BD532" s="14"/>
+      <c r="BG532" s="14"/>
+    </row>
+    <row r="533" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU533" s="14"/>
+      <c r="AW533" s="14"/>
+      <c r="AX533" s="14"/>
+      <c r="BD533" s="14"/>
+      <c r="BF533" s="14"/>
+      <c r="BG533" s="14"/>
+    </row>
+    <row r="534" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU534" s="14"/>
+      <c r="AX534" s="14"/>
+      <c r="BD534" s="14"/>
+      <c r="BG534" s="14"/>
+    </row>
+    <row r="535" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU535" s="14"/>
+      <c r="AW535" s="14"/>
+      <c r="AX535" s="14"/>
+      <c r="BD535" s="14"/>
+      <c r="BF535" s="14"/>
+      <c r="BG535" s="14"/>
+    </row>
+    <row r="536" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU536" s="14"/>
+      <c r="AW536" s="14"/>
+      <c r="AX536" s="14"/>
+      <c r="BD536" s="14"/>
+      <c r="BF536" s="14"/>
+      <c r="BG536" s="14"/>
+    </row>
+    <row r="537" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU537" s="14"/>
+      <c r="AW537" s="14"/>
+      <c r="AX537" s="14"/>
+      <c r="BD537" s="14"/>
+      <c r="BF537" s="14"/>
+      <c r="BG537" s="14"/>
+    </row>
+    <row r="538" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU538" s="14"/>
+      <c r="AX538" s="14"/>
+      <c r="BD538" s="14"/>
+      <c r="BF538" s="14"/>
+      <c r="BG538" s="14"/>
+    </row>
+    <row r="539" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU539" s="14"/>
+      <c r="AX539" s="14"/>
+      <c r="BD539" s="14"/>
+      <c r="BF539" s="14"/>
+      <c r="BG539" s="14"/>
+    </row>
+    <row r="540" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU540" s="14"/>
+      <c r="AX540" s="14"/>
+      <c r="BD540" s="14"/>
+      <c r="BG540" s="14"/>
+    </row>
+    <row r="541" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU541" s="14"/>
+      <c r="AW541" s="14"/>
+      <c r="AX541" s="14"/>
+      <c r="BD541" s="14"/>
+      <c r="BF541" s="14"/>
+      <c r="BG541" s="14"/>
+    </row>
+    <row r="542" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU542" s="14"/>
+      <c r="AW542" s="14"/>
+      <c r="AX542" s="14"/>
+      <c r="BD542" s="14"/>
+      <c r="BF542" s="14"/>
+      <c r="BG542" s="14"/>
+    </row>
+    <row r="543" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU543" s="14"/>
+      <c r="AW543" s="14"/>
+      <c r="AX543" s="14"/>
+      <c r="BD543" s="14"/>
+      <c r="BF543" s="14"/>
+      <c r="BG543" s="14"/>
+    </row>
+    <row r="544" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU544" s="14"/>
+      <c r="AW544" s="14"/>
+      <c r="AX544" s="14"/>
+      <c r="BD544" s="14"/>
+      <c r="BF544" s="14"/>
+      <c r="BG544" s="14"/>
+    </row>
+    <row r="545" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU545" s="14"/>
+      <c r="AW545" s="14"/>
+      <c r="AX545" s="14"/>
+      <c r="BD545" s="14"/>
+      <c r="BF545" s="14"/>
+      <c r="BG545" s="14"/>
+    </row>
+    <row r="546" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU546" s="14"/>
+      <c r="AW546" s="14"/>
+      <c r="AX546" s="14"/>
+      <c r="BD546" s="14"/>
+      <c r="BF546" s="14"/>
+      <c r="BG546" s="14"/>
+    </row>
+    <row r="547" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU547" s="14"/>
+      <c r="AX547" s="14"/>
+      <c r="BD547" s="14"/>
+      <c r="BG547" s="14"/>
+    </row>
+    <row r="548" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU548" s="14"/>
+      <c r="AX548" s="14"/>
+      <c r="BD548" s="14"/>
+      <c r="BG548" s="14"/>
+    </row>
+    <row r="549" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU549" s="14"/>
+      <c r="AX549" s="14"/>
+      <c r="BD549" s="14"/>
+      <c r="BG549" s="14"/>
+    </row>
+    <row r="550" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU550" s="14"/>
+      <c r="AX550" s="14"/>
+      <c r="BD550" s="14"/>
+      <c r="BG550" s="14"/>
+    </row>
+    <row r="551" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU551" s="14"/>
+      <c r="AX551" s="14"/>
+      <c r="BD551" s="14"/>
+      <c r="BG551" s="14"/>
+    </row>
+    <row r="552" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU552" s="14"/>
+      <c r="AX552" s="14"/>
+      <c r="BD552" s="14"/>
+      <c r="BG552" s="14"/>
+    </row>
+    <row r="553" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU553" s="14"/>
+      <c r="AX553" s="14"/>
+      <c r="BD553" s="14"/>
+      <c r="BG553" s="14"/>
+    </row>
+    <row r="554" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU554" s="14"/>
+      <c r="AX554" s="14"/>
+      <c r="BD554" s="14"/>
+      <c r="BG554" s="14"/>
+    </row>
+    <row r="555" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU555" s="14"/>
+      <c r="AX555" s="14"/>
+      <c r="BD555" s="14"/>
+      <c r="BG555" s="14"/>
+    </row>
+    <row r="556" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU556" s="14"/>
+      <c r="AX556" s="14"/>
+      <c r="BD556" s="14"/>
+      <c r="BG556" s="14"/>
+    </row>
+    <row r="557" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU557" s="14"/>
+      <c r="AX557" s="14"/>
+      <c r="BD557" s="14"/>
+      <c r="BG557" s="14"/>
+    </row>
+    <row r="558" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU558" s="14"/>
+      <c r="AX558" s="14"/>
+      <c r="BD558" s="14"/>
+      <c r="BG558" s="14"/>
+    </row>
+    <row r="559" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU559" s="14"/>
+      <c r="AX559" s="14"/>
+      <c r="BD559" s="14"/>
+      <c r="BG559" s="14"/>
+    </row>
+    <row r="560" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU560" s="14"/>
+      <c r="AX560" s="14"/>
+      <c r="BD560" s="14"/>
+      <c r="BG560" s="14"/>
+    </row>
+    <row r="561" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU561" s="14"/>
+      <c r="AX561" s="14"/>
+      <c r="BD561" s="14"/>
+      <c r="BG561" s="14"/>
+    </row>
+    <row r="562" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU562" s="14"/>
+      <c r="AX562" s="14"/>
+      <c r="BD562" s="14"/>
+      <c r="BG562" s="14"/>
+    </row>
+    <row r="563" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU563" s="14"/>
+      <c r="AX563" s="14"/>
+      <c r="BD563" s="14"/>
+      <c r="BG563" s="14"/>
+    </row>
+    <row r="564" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU564" s="14"/>
+      <c r="AX564" s="14"/>
+      <c r="BD564" s="14"/>
+      <c r="BG564" s="14"/>
+    </row>
+    <row r="565" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU565" s="14"/>
+      <c r="AX565" s="14"/>
+      <c r="BD565" s="14"/>
+      <c r="BF565" s="14"/>
+      <c r="BG565" s="14"/>
+    </row>
+    <row r="566" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU566" s="14"/>
+      <c r="AW566" s="14"/>
+      <c r="AX566" s="14"/>
+      <c r="BD566" s="14"/>
+      <c r="BF566" s="14"/>
+      <c r="BG566" s="14"/>
+    </row>
+    <row r="567" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU567" s="14"/>
+      <c r="AW567" s="14"/>
+      <c r="AX567" s="14"/>
+      <c r="BD567" s="14"/>
+      <c r="BF567" s="14"/>
+      <c r="BG567" s="14"/>
+    </row>
+    <row r="568" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU568" s="14"/>
+      <c r="AW568" s="14"/>
+      <c r="AX568" s="14"/>
+      <c r="BD568" s="14"/>
+      <c r="BF568" s="14"/>
+      <c r="BG568" s="14"/>
+    </row>
+    <row r="569" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU569" s="14"/>
+      <c r="AW569" s="14"/>
+      <c r="AX569" s="14"/>
+      <c r="BD569" s="14"/>
+      <c r="BF569" s="14"/>
+      <c r="BG569" s="14"/>
+    </row>
+    <row r="570" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU570" s="14"/>
+      <c r="AX570" s="14"/>
+      <c r="BD570" s="14"/>
+      <c r="BF570" s="14"/>
+      <c r="BG570" s="14"/>
+    </row>
+    <row r="571" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU571" s="14"/>
+      <c r="AX571" s="14"/>
+      <c r="BD571" s="14"/>
+      <c r="BF571" s="14"/>
+      <c r="BG571" s="14"/>
+    </row>
+    <row r="572" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU572" s="14"/>
+      <c r="AX572" s="14"/>
+      <c r="BD572" s="14"/>
+      <c r="BG572" s="14"/>
+    </row>
+    <row r="573" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU573" s="14"/>
+      <c r="AX573" s="14"/>
+      <c r="BD573" s="14"/>
+      <c r="BG573" s="14"/>
+    </row>
+    <row r="574" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU574" s="14"/>
+      <c r="AX574" s="14"/>
+      <c r="BD574" s="14"/>
+      <c r="BG574" s="14"/>
+    </row>
+    <row r="575" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU575" s="14"/>
+      <c r="AX575" s="14"/>
+      <c r="BD575" s="14"/>
+      <c r="BG575" s="14"/>
+    </row>
+    <row r="576" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU576" s="14"/>
+      <c r="AX576" s="14"/>
+      <c r="BD576" s="14"/>
+      <c r="BG576" s="14"/>
+    </row>
+    <row r="577" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU577" s="14"/>
+      <c r="AX577" s="14"/>
+      <c r="BD577" s="14"/>
+      <c r="BG577" s="14"/>
+    </row>
+    <row r="578" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU578" s="14"/>
+      <c r="AX578" s="14"/>
+      <c r="BD578" s="14"/>
+      <c r="BG578" s="14"/>
+    </row>
+    <row r="579" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU579" s="14"/>
+      <c r="AX579" s="14"/>
+      <c r="BD579" s="14"/>
+      <c r="BG579" s="14"/>
+    </row>
+    <row r="580" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU580" s="14"/>
+      <c r="AX580" s="14"/>
+      <c r="BD580" s="14"/>
+      <c r="BG580" s="14"/>
+    </row>
+    <row r="581" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU581" s="14"/>
+      <c r="AX581" s="14"/>
+      <c r="BD581" s="14"/>
+      <c r="BG581" s="14"/>
+    </row>
+    <row r="582" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU582" s="14"/>
+      <c r="AX582" s="14"/>
+      <c r="BD582" s="14"/>
+      <c r="BG582" s="14"/>
+    </row>
+    <row r="583" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU583" s="14"/>
+      <c r="AX583" s="14"/>
+      <c r="BD583" s="14"/>
+      <c r="BG583" s="14"/>
+    </row>
+    <row r="584" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU584" s="14"/>
+      <c r="AX584" s="14"/>
+      <c r="BD584" s="14"/>
+      <c r="BG584" s="14"/>
+    </row>
+    <row r="585" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU585" s="14"/>
+      <c r="AX585" s="14"/>
+      <c r="BD585" s="14"/>
+      <c r="BG585" s="14"/>
+    </row>
+    <row r="586" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU586" s="14"/>
+      <c r="AW586" s="14"/>
+      <c r="AX586" s="14"/>
+      <c r="BD586" s="14"/>
+      <c r="BF586" s="14"/>
+      <c r="BG586" s="14"/>
+    </row>
+    <row r="587" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU587" s="14"/>
+      <c r="AX587" s="14"/>
+      <c r="BD587" s="14"/>
+      <c r="BG587" s="14"/>
+    </row>
+    <row r="588" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU588" s="14"/>
+      <c r="AX588" s="14"/>
+      <c r="BD588" s="14"/>
+      <c r="BG588" s="14"/>
+    </row>
+    <row r="589" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU589" s="14"/>
+      <c r="AX589" s="14"/>
+      <c r="BD589" s="14"/>
+      <c r="BG589" s="14"/>
+    </row>
+    <row r="590" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU590" s="14"/>
+      <c r="AW590" s="14"/>
+      <c r="AX590" s="14"/>
+      <c r="BD590" s="14"/>
+      <c r="BF590" s="14"/>
+      <c r="BG590" s="14"/>
+    </row>
+    <row r="591" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU591" s="14"/>
+      <c r="AW591" s="14"/>
+      <c r="AX591" s="14"/>
+      <c r="BD591" s="14"/>
+      <c r="BF591" s="14"/>
+      <c r="BG591" s="14"/>
+    </row>
+    <row r="592" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU592" s="14"/>
+      <c r="AX592" s="14"/>
+      <c r="BD592" s="14"/>
+      <c r="BG592" s="14"/>
+    </row>
+    <row r="593" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU593" s="14"/>
+      <c r="AX593" s="14"/>
+      <c r="BD593" s="14"/>
+      <c r="BG593" s="14"/>
+    </row>
+    <row r="594" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU594" s="14"/>
+      <c r="AW594" s="14"/>
+      <c r="AX594" s="14"/>
+      <c r="BD594" s="14"/>
+      <c r="BF594" s="14"/>
+      <c r="BG594" s="14"/>
+    </row>
+    <row r="595" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU595" s="14"/>
+      <c r="AX595" s="14"/>
+      <c r="BD595" s="14"/>
+      <c r="BG595" s="14"/>
+    </row>
+    <row r="596" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU596" s="14"/>
+      <c r="AX596" s="14"/>
+      <c r="BD596" s="14"/>
+      <c r="BG596" s="14"/>
+    </row>
+    <row r="597" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU597" s="14"/>
+      <c r="AX597" s="14"/>
+      <c r="BD597" s="14"/>
+      <c r="BG597" s="14"/>
+    </row>
+    <row r="598" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU598" s="14"/>
+      <c r="AX598" s="14"/>
+      <c r="BD598" s="14"/>
+      <c r="BG598" s="14"/>
+    </row>
+    <row r="599" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU599" s="14"/>
+      <c r="AX599" s="14"/>
+      <c r="BD599" s="14"/>
+      <c r="BG599" s="14"/>
+    </row>
+    <row r="600" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU600" s="14"/>
+      <c r="AX600" s="14"/>
+      <c r="BD600" s="14"/>
+      <c r="BG600" s="14"/>
+    </row>
+    <row r="601" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU601" s="14"/>
+      <c r="AX601" s="14"/>
+      <c r="BD601" s="14"/>
+      <c r="BG601" s="14"/>
+    </row>
+    <row r="602" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU602" s="14"/>
+      <c r="AX602" s="14"/>
+      <c r="BD602" s="14"/>
+      <c r="BG602" s="14"/>
+    </row>
+    <row r="603" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU603" s="14"/>
+      <c r="AX603" s="14"/>
+      <c r="BD603" s="14"/>
+      <c r="BG603" s="14"/>
+    </row>
+    <row r="604" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU604" s="14"/>
+      <c r="AX604" s="14"/>
+      <c r="BD604" s="14"/>
+      <c r="BG604" s="14"/>
+    </row>
+    <row r="605" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU605" s="14"/>
+      <c r="AX605" s="14"/>
+      <c r="BD605" s="14"/>
+      <c r="BG605" s="14"/>
+    </row>
+    <row r="606" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU606" s="14"/>
+      <c r="AX606" s="14"/>
+      <c r="BD606" s="14"/>
+      <c r="BF606" s="14"/>
+      <c r="BG606" s="14"/>
+    </row>
+    <row r="607" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU607" s="14"/>
+      <c r="AX607" s="14"/>
+      <c r="BD607" s="14"/>
+      <c r="BG607" s="14"/>
+    </row>
+    <row r="608" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU608" s="14"/>
+      <c r="AX608" s="14"/>
+      <c r="BD608" s="14"/>
+      <c r="BG608" s="14"/>
+    </row>
+    <row r="609" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU609" s="14"/>
+      <c r="AX609" s="14"/>
+      <c r="BD609" s="14"/>
+      <c r="BG609" s="14"/>
+    </row>
+    <row r="610" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU610" s="14"/>
+      <c r="AX610" s="14"/>
+      <c r="BD610" s="14"/>
+      <c r="BG610" s="14"/>
+    </row>
+    <row r="611" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU611" s="14"/>
+      <c r="AW611" s="14"/>
+      <c r="AX611" s="14"/>
+      <c r="BD611" s="14"/>
+      <c r="BF611" s="14"/>
+      <c r="BG611" s="14"/>
+    </row>
+    <row r="612" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU612" s="14"/>
+      <c r="AX612" s="14"/>
+      <c r="BD612" s="14"/>
+      <c r="BG612" s="14"/>
+    </row>
+    <row r="613" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU613" s="14"/>
+      <c r="AX613" s="14"/>
+      <c r="BD613" s="14"/>
+      <c r="BG613" s="14"/>
+    </row>
+    <row r="614" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU614" s="14"/>
+      <c r="AX614" s="14"/>
+      <c r="BD614" s="14"/>
+      <c r="BG614" s="14"/>
+    </row>
+    <row r="615" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU615" s="14"/>
+      <c r="AX615" s="14"/>
+      <c r="BD615" s="14"/>
+      <c r="BG615" s="14"/>
+    </row>
+    <row r="616" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU616" s="14"/>
+      <c r="AX616" s="14"/>
+      <c r="BD616" s="14"/>
+      <c r="BG616" s="14"/>
+    </row>
+    <row r="617" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU617" s="14"/>
+      <c r="AX617" s="14"/>
+      <c r="BD617" s="14"/>
+      <c r="BG617" s="14"/>
+    </row>
+    <row r="618" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU618" s="14"/>
+      <c r="AX618" s="14"/>
+      <c r="BD618" s="14"/>
+      <c r="BG618" s="14"/>
+    </row>
+    <row r="619" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU619" s="14"/>
+      <c r="AX619" s="14"/>
+      <c r="BD619" s="14"/>
+      <c r="BG619" s="14"/>
+    </row>
+    <row r="620" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU620" s="14"/>
+      <c r="AX620" s="14"/>
+      <c r="BD620" s="14"/>
+      <c r="BG620" s="14"/>
+    </row>
+    <row r="621" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU621" s="14"/>
+      <c r="AX621" s="14"/>
+      <c r="BD621" s="14"/>
+      <c r="BG621" s="14"/>
+    </row>
+    <row r="622" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU622" s="14"/>
+      <c r="AX622" s="14"/>
+      <c r="BD622" s="14"/>
+      <c r="BG622" s="14"/>
+    </row>
+    <row r="623" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU623" s="14"/>
+      <c r="AX623" s="14"/>
+      <c r="BD623" s="14"/>
+      <c r="BG623" s="14"/>
+    </row>
+    <row r="624" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU624" s="14"/>
+      <c r="AX624" s="14"/>
+      <c r="BD624" s="14"/>
+      <c r="BG624" s="14"/>
+    </row>
+    <row r="625" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU625" s="14"/>
+      <c r="AX625" s="14"/>
+      <c r="BD625" s="14"/>
+      <c r="BG625" s="14"/>
+    </row>
+    <row r="626" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU626" s="14"/>
+      <c r="AX626" s="14"/>
+      <c r="BD626" s="14"/>
+      <c r="BG626" s="14"/>
+    </row>
+    <row r="627" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU627" s="14"/>
+      <c r="AX627" s="14"/>
+      <c r="BD627" s="14"/>
+      <c r="BG627" s="14"/>
+    </row>
+    <row r="628" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU628" s="14"/>
+      <c r="AX628" s="14"/>
+      <c r="BD628" s="14"/>
+      <c r="BG628" s="14"/>
+    </row>
+    <row r="629" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU629" s="14"/>
+      <c r="AX629" s="14"/>
+      <c r="BD629" s="14"/>
+      <c r="BG629" s="14"/>
+    </row>
+    <row r="630" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU630" s="14"/>
+      <c r="AW630" s="14"/>
+      <c r="AX630" s="14"/>
+      <c r="BD630" s="14"/>
+      <c r="BF630" s="14"/>
+      <c r="BG630" s="14"/>
+    </row>
+    <row r="631" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU631" s="14"/>
+      <c r="AX631" s="14"/>
+      <c r="BD631" s="14"/>
+      <c r="BG631" s="14"/>
+    </row>
+    <row r="632" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU632" s="14"/>
+      <c r="AX632" s="14"/>
+      <c r="BD632" s="14"/>
+      <c r="BG632" s="14"/>
+    </row>
+    <row r="633" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU633" s="14"/>
+      <c r="AX633" s="14"/>
+      <c r="BD633" s="14"/>
+      <c r="BG633" s="14"/>
+    </row>
+    <row r="634" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU634" s="14"/>
+      <c r="AX634" s="14"/>
+      <c r="BD634" s="14"/>
+      <c r="BG634" s="14"/>
+    </row>
+    <row r="635" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU635" s="14"/>
+      <c r="AX635" s="14"/>
+      <c r="BD635" s="14"/>
+      <c r="BG635" s="14"/>
+    </row>
+    <row r="636" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU636" s="14"/>
+      <c r="AX636" s="14"/>
+      <c r="BD636" s="14"/>
+      <c r="BG636" s="14"/>
+    </row>
+    <row r="637" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU637" s="14"/>
+      <c r="AX637" s="14"/>
+      <c r="BD637" s="14"/>
+      <c r="BG637" s="14"/>
+    </row>
+    <row r="638" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU638" s="14"/>
+      <c r="AW638" s="14"/>
+      <c r="AX638" s="14"/>
+      <c r="BD638" s="14"/>
+      <c r="BF638" s="14"/>
+      <c r="BG638" s="14"/>
+    </row>
+    <row r="639" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU639" s="14"/>
+      <c r="AW639" s="14"/>
+      <c r="AX639" s="14"/>
+      <c r="BD639" s="14"/>
+      <c r="BF639" s="14"/>
+      <c r="BG639" s="14"/>
+    </row>
+    <row r="640" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU640" s="14"/>
+      <c r="AW640" s="14"/>
+      <c r="AX640" s="14"/>
+      <c r="BD640" s="14"/>
+      <c r="BF640" s="14"/>
+      <c r="BG640" s="14"/>
+    </row>
+    <row r="641" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU641" s="14"/>
+      <c r="AW641" s="14"/>
+      <c r="AX641" s="14"/>
+      <c r="BD641" s="14"/>
+      <c r="BF641" s="14"/>
+      <c r="BG641" s="14"/>
+    </row>
+    <row r="642" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU642" s="14"/>
+      <c r="AW642" s="14"/>
+      <c r="AX642" s="14"/>
+      <c r="BD642" s="14"/>
+      <c r="BF642" s="14"/>
+      <c r="BG642" s="14"/>
+    </row>
+    <row r="643" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU643" s="14"/>
+      <c r="AW643" s="14"/>
+      <c r="AX643" s="14"/>
+      <c r="BD643" s="14"/>
+      <c r="BF643" s="14"/>
+      <c r="BG643" s="14"/>
+    </row>
+    <row r="644" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU644" s="14"/>
+      <c r="AW644" s="14"/>
+      <c r="AX644" s="14"/>
+      <c r="BD644" s="14"/>
+      <c r="BF644" s="14"/>
+      <c r="BG644" s="14"/>
+    </row>
+    <row r="645" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU645" s="14"/>
+      <c r="AX645" s="14"/>
+      <c r="BD645" s="14"/>
+      <c r="BG645" s="14"/>
+    </row>
+    <row r="646" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU646" s="14"/>
+      <c r="AX646" s="14"/>
+      <c r="BD646" s="14"/>
+      <c r="BG646" s="14"/>
+    </row>
+    <row r="647" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU647" s="14"/>
+      <c r="AX647" s="14"/>
+      <c r="BD647" s="14"/>
+      <c r="BG647" s="14"/>
+    </row>
+    <row r="648" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU648" s="14"/>
+      <c r="AX648" s="14"/>
+      <c r="BD648" s="14"/>
+      <c r="BG648" s="14"/>
+    </row>
+    <row r="649" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU649" s="14"/>
+      <c r="AX649" s="14"/>
+      <c r="BD649" s="14"/>
+      <c r="BG649" s="14"/>
+    </row>
+    <row r="650" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU650" s="14"/>
+      <c r="AX650" s="14"/>
+      <c r="BD650" s="14"/>
+      <c r="BG650" s="14"/>
+    </row>
+    <row r="651" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU651" s="14"/>
+      <c r="AX651" s="14"/>
+      <c r="BD651" s="14"/>
+      <c r="BG651" s="14"/>
+    </row>
+    <row r="652" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU652" s="14"/>
+      <c r="AX652" s="14"/>
+      <c r="BD652" s="14"/>
+      <c r="BG652" s="14"/>
+    </row>
+    <row r="653" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU653" s="14"/>
+      <c r="AX653" s="14"/>
+      <c r="BD653" s="14"/>
+      <c r="BG653" s="14"/>
+    </row>
+    <row r="654" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU654" s="14"/>
+      <c r="AX654" s="14"/>
+      <c r="BD654" s="14"/>
+      <c r="BG654" s="14"/>
+    </row>
+    <row r="655" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU655" s="14"/>
+      <c r="AX655" s="14"/>
+      <c r="BD655" s="14"/>
+      <c r="BG655" s="14"/>
+    </row>
+    <row r="656" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU656" s="14"/>
+      <c r="AX656" s="14"/>
+      <c r="BD656" s="14"/>
+      <c r="BG656" s="14"/>
+    </row>
+    <row r="657" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU657" s="14"/>
+      <c r="AX657" s="14"/>
+      <c r="BD657" s="14"/>
+      <c r="BG657" s="14"/>
+    </row>
+    <row r="658" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU658" s="14"/>
+      <c r="AX658" s="14"/>
+      <c r="BD658" s="14"/>
+      <c r="BG658" s="14"/>
+    </row>
+    <row r="659" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU659" s="14"/>
+      <c r="AX659" s="14"/>
+      <c r="BD659" s="14"/>
+      <c r="BG659" s="14"/>
+    </row>
+    <row r="660" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU660" s="14"/>
+      <c r="AX660" s="14"/>
+      <c r="BD660" s="14"/>
+      <c r="BG660" s="14"/>
+    </row>
+    <row r="661" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU661" s="14"/>
+      <c r="AX661" s="14"/>
+      <c r="BD661" s="14"/>
+      <c r="BG661" s="14"/>
+    </row>
+    <row r="662" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU662" s="14"/>
+      <c r="AX662" s="14"/>
+      <c r="BD662" s="14"/>
+      <c r="BG662" s="14"/>
+    </row>
+    <row r="663" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU663" s="14"/>
+      <c r="AX663" s="14"/>
+      <c r="BD663" s="14"/>
+      <c r="BG663" s="14"/>
+    </row>
+    <row r="664" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU664" s="14"/>
+      <c r="AX664" s="14"/>
+      <c r="BD664" s="14"/>
+      <c r="BG664" s="14"/>
+    </row>
+    <row r="665" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU665" s="14"/>
+      <c r="AX665" s="14"/>
+      <c r="BD665" s="14"/>
+      <c r="BG665" s="14"/>
+    </row>
+    <row r="666" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU666" s="14"/>
+      <c r="AW666" s="14"/>
+      <c r="AX666" s="14"/>
+      <c r="BD666" s="14"/>
+      <c r="BF666" s="14"/>
+      <c r="BG666" s="14"/>
+    </row>
+    <row r="667" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU667" s="14"/>
+      <c r="AX667" s="14"/>
+      <c r="BD667" s="14"/>
+      <c r="BG667" s="14"/>
+    </row>
+    <row r="668" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU668" s="14"/>
+      <c r="AX668" s="14"/>
+      <c r="BD668" s="14"/>
+      <c r="BG668" s="14"/>
+    </row>
+    <row r="669" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU669" s="14"/>
+      <c r="AX669" s="14"/>
+      <c r="BD669" s="14"/>
+      <c r="BG669" s="14"/>
+    </row>
+    <row r="670" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU670" s="14"/>
+      <c r="AX670" s="14"/>
+      <c r="BD670" s="14"/>
+      <c r="BG670" s="14"/>
+    </row>
+    <row r="671" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU671" s="14"/>
+      <c r="AX671" s="14"/>
+      <c r="BD671" s="14"/>
+      <c r="BG671" s="14"/>
+    </row>
+    <row r="672" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU672" s="14"/>
+      <c r="AX672" s="14"/>
+      <c r="BD672" s="14"/>
+      <c r="BG672" s="14"/>
+    </row>
+    <row r="673" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU673" s="14"/>
+      <c r="AX673" s="14"/>
+      <c r="BD673" s="14"/>
+      <c r="BG673" s="14"/>
+    </row>
+    <row r="674" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU674" s="14"/>
+      <c r="AX674" s="14"/>
+      <c r="BD674" s="14"/>
+      <c r="BG674" s="14"/>
+    </row>
+    <row r="675" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU675" s="14"/>
+      <c r="AX675" s="14"/>
+      <c r="BD675" s="14"/>
+      <c r="BG675" s="14"/>
+    </row>
+    <row r="676" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU676" s="14"/>
+      <c r="AX676" s="14"/>
+      <c r="BD676" s="14"/>
+      <c r="BG676" s="14"/>
+    </row>
+    <row r="677" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU677" s="14"/>
+      <c r="AX677" s="14"/>
+      <c r="BD677" s="14"/>
+      <c r="BG677" s="14"/>
+    </row>
+    <row r="678" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU678" s="14"/>
+      <c r="AX678" s="14"/>
+      <c r="BD678" s="14"/>
+      <c r="BG678" s="14"/>
+    </row>
+    <row r="679" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU679" s="14"/>
+      <c r="AX679" s="14"/>
+      <c r="BD679" s="14"/>
+      <c r="BG679" s="14"/>
+    </row>
+    <row r="680" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU680" s="14"/>
+      <c r="AW680" s="14"/>
+      <c r="AX680" s="14"/>
+      <c r="BD680" s="14"/>
+      <c r="BF680" s="14"/>
+      <c r="BG680" s="14"/>
+    </row>
+    <row r="681" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU681" s="14"/>
+      <c r="AW681" s="14"/>
+      <c r="AX681" s="14"/>
+      <c r="BD681" s="14"/>
+      <c r="BF681" s="14"/>
+      <c r="BG681" s="14"/>
+    </row>
+    <row r="682" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU682" s="14"/>
+      <c r="AX682" s="14"/>
+      <c r="BD682" s="14"/>
+      <c r="BG682" s="14"/>
+    </row>
+    <row r="683" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU683" s="14"/>
+      <c r="AX683" s="14"/>
+      <c r="BD683" s="14"/>
+      <c r="BG683" s="14"/>
+    </row>
+    <row r="684" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU684" s="14"/>
+      <c r="AX684" s="14"/>
+      <c r="BD684" s="14"/>
+      <c r="BG684" s="14"/>
+    </row>
+    <row r="685" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU685" s="14"/>
+      <c r="AX685" s="14"/>
+      <c r="BD685" s="14"/>
+      <c r="BG685" s="14"/>
+    </row>
+    <row r="686" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU686" s="14"/>
+      <c r="AX686" s="14"/>
+      <c r="BD686" s="14"/>
+      <c r="BG686" s="14"/>
+    </row>
+    <row r="687" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU687" s="14"/>
+      <c r="AX687" s="14"/>
+      <c r="BD687" s="14"/>
+      <c r="BG687" s="14"/>
+    </row>
+    <row r="688" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU688" s="14"/>
+      <c r="AX688" s="14"/>
+      <c r="BD688" s="14"/>
+      <c r="BG688" s="14"/>
+    </row>
+    <row r="689" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU689" s="14"/>
+      <c r="AX689" s="14"/>
+      <c r="BD689" s="14"/>
+      <c r="BG689" s="14"/>
+    </row>
+    <row r="690" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU690" s="14"/>
+      <c r="AX690" s="14"/>
+      <c r="BD690" s="14"/>
+      <c r="BG690" s="14"/>
+    </row>
+    <row r="691" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU691" s="14"/>
+      <c r="AX691" s="14"/>
+      <c r="BD691" s="14"/>
+      <c r="BG691" s="14"/>
+    </row>
+    <row r="692" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU692" s="14"/>
+      <c r="AX692" s="14"/>
+      <c r="BD692" s="14"/>
+      <c r="BG692" s="14"/>
+    </row>
+    <row r="693" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU693" s="14"/>
+      <c r="AX693" s="14"/>
+      <c r="BD693" s="14"/>
+      <c r="BG693" s="14"/>
+    </row>
+    <row r="694" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU694" s="14"/>
+      <c r="AX694" s="14"/>
+      <c r="BD694" s="14"/>
+      <c r="BG694" s="14"/>
+    </row>
+    <row r="695" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU695" s="14"/>
+      <c r="AX695" s="14"/>
+      <c r="BD695" s="14"/>
+      <c r="BG695" s="14"/>
+    </row>
+    <row r="696" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU696" s="14"/>
+      <c r="AX696" s="14"/>
+      <c r="BD696" s="14"/>
+      <c r="BG696" s="14"/>
+    </row>
+    <row r="697" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU697" s="14"/>
+      <c r="AX697" s="14"/>
+      <c r="BD697" s="14"/>
+      <c r="BG697" s="14"/>
+    </row>
+    <row r="698" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU698" s="14"/>
+      <c r="AX698" s="14"/>
+      <c r="BD698" s="14"/>
+      <c r="BG698" s="14"/>
+    </row>
+    <row r="699" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU699" s="14"/>
+      <c r="AX699" s="14"/>
+      <c r="BD699" s="14"/>
+      <c r="BG699" s="14"/>
+    </row>
+    <row r="700" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU700" s="14"/>
+      <c r="AX700" s="14"/>
+      <c r="BD700" s="14"/>
+      <c r="BG700" s="14"/>
+    </row>
+    <row r="701" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU701" s="14"/>
+      <c r="AX701" s="14"/>
+      <c r="BD701" s="14"/>
+      <c r="BG701" s="14"/>
+    </row>
+    <row r="702" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU702" s="14"/>
+      <c r="AX702" s="14"/>
+      <c r="BD702" s="14"/>
+      <c r="BG702" s="14"/>
+    </row>
+    <row r="703" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU703" s="14"/>
+      <c r="AW703" s="14"/>
+      <c r="AX703" s="14"/>
+      <c r="BD703" s="14"/>
+      <c r="BF703" s="14"/>
+      <c r="BG703" s="14"/>
+    </row>
+    <row r="704" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU704" s="14"/>
+      <c r="AX704" s="14"/>
+      <c r="BD704" s="14"/>
+      <c r="BG704" s="14"/>
+    </row>
+    <row r="705" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU705" s="14"/>
+      <c r="AX705" s="14"/>
+      <c r="BD705" s="14"/>
+      <c r="BG705" s="14"/>
+    </row>
+    <row r="706" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU706" s="14"/>
+      <c r="AX706" s="14"/>
+      <c r="BD706" s="14"/>
+      <c r="BG706" s="14"/>
+    </row>
+    <row r="707" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU707" s="14"/>
+      <c r="AX707" s="14"/>
+      <c r="BD707" s="14"/>
+      <c r="BG707" s="14"/>
+    </row>
+    <row r="708" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU708" s="14"/>
+      <c r="AX708" s="14"/>
+      <c r="BD708" s="14"/>
+      <c r="BG708" s="14"/>
+    </row>
+    <row r="709" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU709" s="14"/>
+      <c r="AX709" s="14"/>
+      <c r="BD709" s="14"/>
+      <c r="BG709" s="14"/>
+    </row>
+    <row r="710" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU710" s="14"/>
+      <c r="AX710" s="14"/>
+      <c r="BD710" s="14"/>
+      <c r="BG710" s="14"/>
+    </row>
+    <row r="711" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU711" s="14"/>
+      <c r="AX711" s="14"/>
+      <c r="BD711" s="14"/>
+      <c r="BG711" s="14"/>
+    </row>
+    <row r="712" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU712" s="14"/>
+      <c r="AX712" s="14"/>
+      <c r="BD712" s="14"/>
+      <c r="BG712" s="14"/>
+    </row>
+    <row r="713" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU713" s="14"/>
+      <c r="AX713" s="14"/>
+      <c r="BD713" s="14"/>
+      <c r="BG713" s="14"/>
+    </row>
+    <row r="714" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU714" s="14"/>
+      <c r="AX714" s="14"/>
+      <c r="BD714" s="14"/>
+      <c r="BG714" s="14"/>
+    </row>
+    <row r="715" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU715" s="14"/>
+      <c r="AX715" s="14"/>
+      <c r="BD715" s="14"/>
+      <c r="BG715" s="14"/>
+    </row>
+    <row r="716" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU716" s="14"/>
+      <c r="AX716" s="14"/>
+      <c r="BD716" s="14"/>
+      <c r="BG716" s="14"/>
+    </row>
+    <row r="717" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU717" s="14"/>
+      <c r="AX717" s="14"/>
+      <c r="BD717" s="14"/>
+      <c r="BG717" s="14"/>
+    </row>
+    <row r="718" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU718" s="14"/>
+      <c r="AX718" s="14"/>
+      <c r="BD718" s="14"/>
+      <c r="BG718" s="14"/>
+    </row>
+    <row r="719" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU719" s="14"/>
+      <c r="AX719" s="14"/>
+      <c r="BD719" s="14"/>
+      <c r="BG719" s="14"/>
+    </row>
+    <row r="720" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU720" s="14"/>
+      <c r="AX720" s="14"/>
+      <c r="BD720" s="14"/>
+      <c r="BG720" s="14"/>
+    </row>
+    <row r="721" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU721" s="14"/>
+      <c r="AX721" s="14"/>
+      <c r="BD721" s="14"/>
+      <c r="BG721" s="14"/>
+    </row>
+    <row r="722" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU722" s="14"/>
+      <c r="AX722" s="14"/>
+      <c r="BD722" s="14"/>
+      <c r="BG722" s="14"/>
+    </row>
+    <row r="723" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU723" s="14"/>
+      <c r="AX723" s="14"/>
+      <c r="BD723" s="14"/>
+      <c r="BF723" s="14"/>
+      <c r="BG723" s="14"/>
+    </row>
+    <row r="724" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU724" s="14"/>
+      <c r="AX724" s="14"/>
+      <c r="BD724" s="14"/>
+      <c r="BG724" s="14"/>
+    </row>
+    <row r="725" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU725" s="14"/>
+      <c r="AX725" s="14"/>
+      <c r="BD725" s="14"/>
+      <c r="BG725" s="14"/>
+    </row>
+    <row r="726" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU726" s="14"/>
+      <c r="AX726" s="14"/>
+      <c r="BD726" s="14"/>
+      <c r="BG726" s="14"/>
+    </row>
+    <row r="727" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU727" s="14"/>
+      <c r="AX727" s="14"/>
+      <c r="BD727" s="14"/>
+      <c r="BG727" s="14"/>
+    </row>
+    <row r="728" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU728" s="14"/>
+      <c r="AX728" s="14"/>
+      <c r="BD728" s="14"/>
+      <c r="BG728" s="14"/>
+    </row>
+    <row r="729" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU729" s="14"/>
+      <c r="AX729" s="14"/>
+      <c r="BD729" s="14"/>
+      <c r="BG729" s="14"/>
+    </row>
+    <row r="730" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU730" s="14"/>
+      <c r="AX730" s="14"/>
+      <c r="BD730" s="14"/>
+      <c r="BG730" s="14"/>
+    </row>
+    <row r="731" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU731" s="14"/>
+      <c r="AX731" s="14"/>
+      <c r="BD731" s="14"/>
+      <c r="BG731" s="14"/>
+    </row>
+    <row r="732" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU732" s="14"/>
+      <c r="AX732" s="14"/>
+      <c r="BD732" s="14"/>
+      <c r="BG732" s="14"/>
+    </row>
+    <row r="733" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU733" s="14"/>
+      <c r="AX733" s="14"/>
+      <c r="BD733" s="14"/>
+      <c r="BG733" s="14"/>
+    </row>
+    <row r="734" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU734" s="14"/>
+      <c r="AX734" s="14"/>
+      <c r="BD734" s="14"/>
+      <c r="BG734" s="14"/>
+    </row>
+    <row r="735" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU735" s="14"/>
+      <c r="AX735" s="14"/>
+      <c r="BD735" s="14"/>
+      <c r="BG735" s="14"/>
+    </row>
+    <row r="736" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU736" s="14"/>
+      <c r="AX736" s="14"/>
+      <c r="BD736" s="14"/>
+      <c r="BG736" s="14"/>
+    </row>
+    <row r="737" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU737" s="14"/>
+      <c r="AX737" s="14"/>
+      <c r="BD737" s="14"/>
+      <c r="BG737" s="14"/>
+    </row>
+    <row r="738" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU738" s="14"/>
+      <c r="AX738" s="14"/>
+      <c r="BD738" s="14"/>
+      <c r="BG738" s="14"/>
+    </row>
+    <row r="739" spans="47:59" x14ac:dyDescent="0.3">
+      <c r="AU739" s="14"/>
+      <c r="AX739" s="14"/>
+      <c r="BD739" s="14"/>
+      <c r="BG739" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11CFE3D-18E8-4407-BE68-1F5609022012}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="19.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <conditionalFormatting sqref="E1:P1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Inactive">
+      <formula>NOT(ISERROR(SEARCH("Inactive",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Exited">
+      <formula>NOT(ISERROR(SEARCH("Exited",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Homeless">
+      <formula>NOT(ISERROR(SEARCH("Homeless",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Housed">
+      <formula>NOT(ISERROR(SEARCH("Housed",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F67DAF-B8F5-4C44-B5C7-217B0CCD2D1B}">
+  <dimension ref="D1:G150"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:7" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+    </row>
+    <row r="43" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+    </row>
+    <row r="44" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="45" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+    </row>
+    <row r="47" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+    </row>
+    <row r="48" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+    </row>
+    <row r="51" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+    </row>
+    <row r="52" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+    </row>
+    <row r="53" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+    </row>
+    <row r="54" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+    </row>
+    <row r="55" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+    </row>
+    <row r="56" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+    </row>
+    <row r="57" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+    </row>
+    <row r="58" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+    </row>
+    <row r="59" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+    </row>
+    <row r="60" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+    </row>
+    <row r="61" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+    </row>
+    <row r="62" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+    </row>
+    <row r="63" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+    </row>
+    <row r="64" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+    </row>
+    <row r="65" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+    </row>
+    <row r="66" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+    </row>
+    <row r="67" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+    </row>
+    <row r="68" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+    </row>
+    <row r="69" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+    </row>
+    <row r="70" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+    </row>
+    <row r="71" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+    </row>
+    <row r="72" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+    </row>
+    <row r="73" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+    </row>
+    <row r="74" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+    </row>
+    <row r="75" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+    </row>
+    <row r="76" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+    </row>
+    <row r="77" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+    </row>
+    <row r="78" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+    </row>
+    <row r="79" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+    </row>
+    <row r="80" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+    </row>
+    <row r="81" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+    </row>
+    <row r="82" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+    </row>
+    <row r="83" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+    </row>
+    <row r="84" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+    </row>
+    <row r="85" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+    </row>
+    <row r="86" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+    </row>
+    <row r="87" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+    </row>
+    <row r="88" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+    </row>
+    <row r="89" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+    </row>
+    <row r="90" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+    </row>
+    <row r="91" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+    </row>
+    <row r="92" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+    </row>
+    <row r="93" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+    </row>
+    <row r="94" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
+    </row>
+    <row r="95" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+    </row>
+    <row r="96" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+    </row>
+    <row r="97" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+    </row>
+    <row r="98" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+    </row>
+    <row r="99" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+    </row>
+    <row r="100" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+    </row>
+    <row r="101" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D101" s="14"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+    </row>
+    <row r="102" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D102" s="14"/>
+      <c r="E102" s="14"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+    </row>
+    <row r="103" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D103" s="14"/>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+    </row>
+    <row r="104" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
+    </row>
+    <row r="105" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+    </row>
+    <row r="106" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+    </row>
+    <row r="107" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+    </row>
+    <row r="108" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+    </row>
+    <row r="109" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
+    </row>
+    <row r="110" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+    </row>
+    <row r="111" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+    </row>
+    <row r="112" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+    </row>
+    <row r="113" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
+    </row>
+    <row r="114" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+    </row>
+    <row r="115" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+    </row>
+    <row r="116" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+    </row>
+    <row r="117" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D117" s="14"/>
+      <c r="E117" s="14"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+    </row>
+    <row r="118" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D118" s="14"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+    </row>
+    <row r="119" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D119" s="14"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+    </row>
+    <row r="120" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D120" s="14"/>
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
+    </row>
+    <row r="121" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D121" s="14"/>
+      <c r="E121" s="14"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
+    </row>
+    <row r="122" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D122" s="14"/>
+      <c r="E122" s="14"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14"/>
+    </row>
+    <row r="123" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D123" s="14"/>
+      <c r="E123" s="14"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="14"/>
+    </row>
+    <row r="124" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D124" s="14"/>
+      <c r="E124" s="14"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="14"/>
+    </row>
+    <row r="125" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D125" s="14"/>
+      <c r="E125" s="14"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="14"/>
+    </row>
+    <row r="126" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D126" s="14"/>
+      <c r="E126" s="14"/>
+      <c r="F126" s="14"/>
+      <c r="G126" s="14"/>
+    </row>
+    <row r="127" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D127" s="14"/>
+      <c r="E127" s="14"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="14"/>
+    </row>
+    <row r="128" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D128" s="14"/>
+      <c r="E128" s="14"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="14"/>
+    </row>
+    <row r="129" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D129" s="14"/>
+      <c r="E129" s="14"/>
+      <c r="F129" s="14"/>
+      <c r="G129" s="14"/>
+    </row>
+    <row r="130" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D130" s="14"/>
+      <c r="E130" s="14"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="14"/>
+    </row>
+    <row r="131" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D131" s="14"/>
+      <c r="E131" s="14"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="14"/>
+    </row>
+    <row r="132" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D132" s="14"/>
+      <c r="E132" s="14"/>
+      <c r="F132" s="14"/>
+      <c r="G132" s="14"/>
+    </row>
+    <row r="133" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D133" s="14"/>
+      <c r="E133" s="14"/>
+      <c r="F133" s="14"/>
+      <c r="G133" s="14"/>
+    </row>
+    <row r="134" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D134" s="14"/>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="14"/>
+    </row>
+    <row r="135" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D135" s="14"/>
+      <c r="E135" s="14"/>
+      <c r="F135" s="14"/>
+      <c r="G135" s="14"/>
+    </row>
+    <row r="136" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D136" s="14"/>
+      <c r="E136" s="14"/>
+      <c r="F136" s="14"/>
+      <c r="G136" s="14"/>
+    </row>
+    <row r="137" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D137" s="14"/>
+      <c r="E137" s="14"/>
+      <c r="F137" s="14"/>
+      <c r="G137" s="14"/>
+    </row>
+    <row r="138" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D138" s="14"/>
+      <c r="E138" s="14"/>
+      <c r="F138" s="14"/>
+      <c r="G138" s="14"/>
+    </row>
+    <row r="139" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D139" s="14"/>
+      <c r="E139" s="14"/>
+      <c r="F139" s="14"/>
+      <c r="G139" s="14"/>
+    </row>
+    <row r="140" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D140" s="14"/>
+      <c r="E140" s="14"/>
+      <c r="F140" s="14"/>
+      <c r="G140" s="14"/>
+    </row>
+    <row r="141" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D141" s="14"/>
+      <c r="E141" s="14"/>
+      <c r="F141" s="14"/>
+      <c r="G141" s="14"/>
+    </row>
+    <row r="142" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D142" s="14"/>
+      <c r="E142" s="14"/>
+      <c r="F142" s="14"/>
+      <c r="G142" s="14"/>
+    </row>
+    <row r="143" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D143" s="14"/>
+      <c r="E143" s="14"/>
+      <c r="F143" s="14"/>
+      <c r="G143" s="14"/>
+    </row>
+    <row r="144" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D144" s="14"/>
+      <c r="E144" s="14"/>
+      <c r="F144" s="14"/>
+      <c r="G144" s="14"/>
+    </row>
+    <row r="145" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D145" s="14"/>
+      <c r="E145" s="14"/>
+      <c r="F145" s="14"/>
+      <c r="G145" s="14"/>
+    </row>
+    <row r="146" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D146" s="14"/>
+      <c r="E146" s="14"/>
+      <c r="F146" s="14"/>
+      <c r="G146" s="14"/>
+    </row>
+    <row r="147" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D147" s="14"/>
+      <c r="E147" s="14"/>
+      <c r="F147" s="14"/>
+      <c r="G147" s="14"/>
+    </row>
+    <row r="148" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D148" s="14"/>
+      <c r="E148" s="14"/>
+      <c r="F148" s="14"/>
+      <c r="G148" s="14"/>
+    </row>
+    <row r="149" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D149" s="14"/>
+      <c r="E149" s="14"/>
+      <c r="F149" s="14"/>
+      <c r="G149" s="14"/>
+    </row>
+    <row r="150" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D150" s="14"/>
+      <c r="E150" s="14"/>
+      <c r="F150" s="14"/>
+      <c r="G150" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/www/CLE Instructions and Data Dictionary.xlsx
+++ b/www/CLE Instructions and Data Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\projects\CE_Data_Toolkit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE5F895-089F-452D-80B3-74732EC7DA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FC8678-A985-46AF-BCC0-C9C9F4153BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3912" yWindow="1680" windowWidth="17280" windowHeight="9024" firstSheet="1" activeTab="1" xr2:uid="{51E25282-ACA6-44F1-BA60-C197611A1412}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="9024" firstSheet="1" activeTab="1" xr2:uid="{51E25282-ACA6-44F1-BA60-C197611A1412}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="4" r:id="rId1"/>
@@ -594,9 +594,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">4) Monthly Statuses </t>
-  </si>
-  <si>
     <t>The Monthly Statuses tab shows who was housed during the report period, who had at least one system exit to permanent housing during the report period, and the end-of-the-month system status for every client included in the Client Details tab. This allows users to see client outcomes, highlighting changes in system status over the report period. There is one row per client. A blank monthly status indicates the client was not active during that month.</t>
   </si>
   <si>
@@ -643,9 +640,6 @@
       </rPr>
       <t>identifies clients who either moved into housing or exited the system to a permanent destination by the end of the report period</t>
     </r>
-  </si>
-  <si>
-    <t>5) Adjusted Enrollments</t>
   </si>
   <si>
     <t>This tab lists enrollments that had date adjusments for the purposes of Eva's system performance logic. For example, non-residential enrollments without an Exit Date during the report period had their Exit Date reset with a buffer after theEntry Date or last Current Living Situation record (whichever was later).</t>
@@ -867,6 +861,12 @@
   </si>
   <si>
     <t>LH_Dates is an Eva-defined variable. This field lists dates during the enrollment where the client was experincing literal homelessness. Dates may include an Entry Date with a literally homeless Prior Living Situation, Bed-Night Dates for night-by-night enrollments, and Current Living Situation records with a literally homeless living situation.</t>
+  </si>
+  <si>
+    <t>4) Monthly Statuses (System Overview Only)</t>
+  </si>
+  <si>
+    <t>5) Adjusted Enrollments (System Overview Only)</t>
   </si>
 </sst>
 </file>
@@ -1483,19 +1483,12 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1511,11 +1504,18 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="34" spans="1:2" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="B34" s="8"/>
     </row>
     <row r="35" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" s="8"/>
     </row>
@@ -2069,19 +2069,19 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B38" s="8"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B39" s="8"/>
     </row>
     <row r="40" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B40" s="8"/>
     </row>
@@ -2091,13 +2091,13 @@
     </row>
     <row r="42" spans="1:2" ht="18" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="B42" s="8"/>
     </row>
     <row r="43" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B43" s="8"/>
     </row>
@@ -2113,13 +2113,13 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B46" s="8"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B47" s="8"/>
     </row>
@@ -2224,13 +2224,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2290,13 +2290,13 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2312,13 +2312,13 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2334,24 +2334,24 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2367,13 +2367,13 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2389,13 +2389,13 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2411,35 +2411,35 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B27" t="s">
         <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2499,13 +2499,13 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2543,35 +2543,35 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -2670,7 +2670,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2703,7 +2703,7 @@
         <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2714,7 +2714,7 @@
         <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2769,7 +2769,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
         <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -2813,29 +2813,29 @@
         <v>80</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>158</v>
+      </c>
+      <c r="B62" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" t="s">
         <v>160</v>
-      </c>
-      <c r="B62" t="s">
-        <v>161</v>
-      </c>
-      <c r="C62" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C63" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -7671,16 +7671,16 @@
     <row r="1" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="E1:P1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Inactive">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Inactive">
       <formula>NOT(ISERROR(SEARCH("Inactive",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Exited">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Exited">
       <formula>NOT(ISERROR(SEARCH("Exited",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Homeless">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Homeless">
       <formula>NOT(ISERROR(SEARCH("Homeless",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Housed">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Housed">
       <formula>NOT(ISERROR(SEARCH("Housed",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
